--- a/events/LaSeu_2022_WC/LaSeu_2022_WC_start.xlsx
+++ b/events/LaSeu_2022_WC/LaSeu_2022_WC_start.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W709"/>
+  <dimension ref="A1:AC709"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -519,17 +519,47 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>Name4</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Name5</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>Name6</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
           <t>ICF_ID1</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>ICF_ID2</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>ICF_ID3</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>ICF_ID4</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>ICF_ID5</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>ICF_ID6</t>
         </is>
       </c>
     </row>
@@ -1545,7 +1575,7 @@
           <t>CHOU Chih-Chin</t>
         </is>
       </c>
-      <c r="U22" t="inlineStr">
+      <c r="X22" t="inlineStr">
         <is>
           <t>68975</t>
         </is>
@@ -1603,7 +1633,7 @@
           <t>PISTONI Lucia</t>
         </is>
       </c>
-      <c r="U23" t="inlineStr">
+      <c r="X23" t="inlineStr">
         <is>
           <t>104430</t>
         </is>
@@ -1661,7 +1691,7 @@
           <t>SOMMERNES Iris</t>
         </is>
       </c>
-      <c r="U24" t="inlineStr">
+      <c r="X24" t="inlineStr">
         <is>
           <t>90378</t>
         </is>
@@ -1719,7 +1749,7 @@
           <t>ZOU Xiaolin</t>
         </is>
       </c>
-      <c r="U25" t="inlineStr">
+      <c r="X25" t="inlineStr">
         <is>
           <t>118854</t>
         </is>
@@ -1777,7 +1807,7 @@
           <t>SPICER Phoebe</t>
         </is>
       </c>
-      <c r="U26" t="inlineStr">
+      <c r="X26" t="inlineStr">
         <is>
           <t>75827</t>
         </is>
@@ -1835,7 +1865,7 @@
           <t>JODAR Celia</t>
         </is>
       </c>
-      <c r="U27" t="inlineStr">
+      <c r="X27" t="inlineStr">
         <is>
           <t>36936</t>
         </is>
@@ -1893,7 +1923,7 @@
           <t>RAZEGHIAN Roxana</t>
         </is>
       </c>
-      <c r="U28" t="inlineStr">
+      <c r="X28" t="inlineStr">
         <is>
           <t>63124</t>
         </is>
@@ -1951,7 +1981,7 @@
           <t>RIQUELME Nadia</t>
         </is>
       </c>
-      <c r="U29" t="inlineStr">
+      <c r="X29" t="inlineStr">
         <is>
           <t>41626</t>
         </is>
@@ -2009,7 +2039,7 @@
           <t>CASSINI Maria Luz</t>
         </is>
       </c>
-      <c r="U30" t="inlineStr">
+      <c r="X30" t="inlineStr">
         <is>
           <t>41627</t>
         </is>
@@ -2067,7 +2097,7 @@
           <t>REINOSO Sofia</t>
         </is>
       </c>
-      <c r="U31" t="inlineStr">
+      <c r="X31" t="inlineStr">
         <is>
           <t>45745</t>
         </is>
@@ -2125,7 +2155,7 @@
           <t>BRZESKA Dominika</t>
         </is>
       </c>
-      <c r="U32" t="inlineStr">
+      <c r="X32" t="inlineStr">
         <is>
           <t>93913</t>
         </is>
@@ -2183,7 +2213,7 @@
           <t>MISHIMA Ren</t>
         </is>
       </c>
-      <c r="U33" t="inlineStr">
+      <c r="X33" t="inlineStr">
         <is>
           <t>37757</t>
         </is>
@@ -2241,7 +2271,7 @@
           <t>ITO Kurumi</t>
         </is>
       </c>
-      <c r="U34" t="inlineStr">
+      <c r="X34" t="inlineStr">
         <is>
           <t>83683</t>
         </is>
@@ -2299,7 +2329,7 @@
           <t>GLEJTEKOVA Simona</t>
         </is>
       </c>
-      <c r="U35" t="inlineStr">
+      <c r="X35" t="inlineStr">
         <is>
           <t>55166</t>
         </is>
@@ -2357,7 +2387,7 @@
           <t>COLLIN Georgina</t>
         </is>
       </c>
-      <c r="U36" t="inlineStr">
+      <c r="X36" t="inlineStr">
         <is>
           <t>60108</t>
         </is>
@@ -2415,7 +2445,7 @@
           <t>BALDONI Lea</t>
         </is>
       </c>
-      <c r="U37" t="inlineStr">
+      <c r="X37" t="inlineStr">
         <is>
           <t>94529</t>
         </is>
@@ -2473,7 +2503,7 @@
           <t>KRIESINGER Janina</t>
         </is>
       </c>
-      <c r="U38" t="inlineStr">
+      <c r="X38" t="inlineStr">
         <is>
           <t>93682</t>
         </is>
@@ -2531,7 +2561,7 @@
           <t>APEL Emily</t>
         </is>
       </c>
-      <c r="U39" t="inlineStr">
+      <c r="X39" t="inlineStr">
         <is>
           <t>83788</t>
         </is>
@@ -2589,7 +2619,7 @@
           <t>CUCHI Julia</t>
         </is>
       </c>
-      <c r="U40" t="inlineStr">
+      <c r="X40" t="inlineStr">
         <is>
           <t>35764</t>
         </is>
@@ -2647,7 +2677,7 @@
           <t>BETTERIDGE Lois</t>
         </is>
       </c>
-      <c r="U41" t="inlineStr">
+      <c r="X41" t="inlineStr">
         <is>
           <t>60078</t>
         </is>
@@ -2705,7 +2735,7 @@
           <t>MAHEU Florence</t>
         </is>
       </c>
-      <c r="U42" t="inlineStr">
+      <c r="X42" t="inlineStr">
         <is>
           <t>36416</t>
         </is>
@@ -2763,7 +2793,7 @@
           <t>PELLICER CHICA Laura</t>
         </is>
       </c>
-      <c r="U43" t="inlineStr">
+      <c r="X43" t="inlineStr">
         <is>
           <t>43129</t>
         </is>
@@ -2821,7 +2851,7 @@
           <t>WILLIAMS Courtney</t>
         </is>
       </c>
-      <c r="U44" t="inlineStr">
+      <c r="X44" t="inlineStr">
         <is>
           <t>68771</t>
         </is>
@@ -2879,7 +2909,7 @@
           <t>LEENDERS Claudia</t>
         </is>
       </c>
-      <c r="U45" t="inlineStr">
+      <c r="X45" t="inlineStr">
         <is>
           <t>35331</t>
         </is>
@@ -2937,7 +2967,7 @@
           <t>YAN Jiahua</t>
         </is>
       </c>
-      <c r="U46" t="inlineStr">
+      <c r="X46" t="inlineStr">
         <is>
           <t>43545</t>
         </is>
@@ -2995,7 +3025,7 @@
           <t>SRIBAR Ria</t>
         </is>
       </c>
-      <c r="U47" t="inlineStr">
+      <c r="X47" t="inlineStr">
         <is>
           <t>75645</t>
         </is>
@@ -3053,7 +3083,7 @@
           <t>THOMAS Hannah</t>
         </is>
       </c>
-      <c r="U48" t="inlineStr">
+      <c r="X48" t="inlineStr">
         <is>
           <t>85758</t>
         </is>
@@ -3111,7 +3141,7 @@
           <t>MARX Alena</t>
         </is>
       </c>
-      <c r="U49" t="inlineStr">
+      <c r="X49" t="inlineStr">
         <is>
           <t>68844</t>
         </is>
@@ -3169,7 +3199,7 @@
           <t>LI Tong</t>
         </is>
       </c>
-      <c r="U50" t="inlineStr">
+      <c r="X50" t="inlineStr">
         <is>
           <t>52023</t>
         </is>
@@ -3227,7 +3257,7 @@
           <t>PANKOVA Zuzana</t>
         </is>
       </c>
-      <c r="U51" t="inlineStr">
+      <c r="X51" t="inlineStr">
         <is>
           <t>93906</t>
         </is>
@@ -3285,7 +3315,7 @@
           <t>BOUZIDI Carole</t>
         </is>
       </c>
-      <c r="U52" t="inlineStr">
+      <c r="X52" t="inlineStr">
         <is>
           <t>118428</t>
         </is>
@@ -3343,7 +3373,7 @@
           <t>TEUNISSEN Lena</t>
         </is>
       </c>
-      <c r="U53" t="inlineStr">
+      <c r="X53" t="inlineStr">
         <is>
           <t>35344</t>
         </is>
@@ -3401,7 +3431,7 @@
           <t>BERTONCELLI Marta</t>
         </is>
       </c>
-      <c r="U54" t="inlineStr">
+      <c r="X54" t="inlineStr">
         <is>
           <t>71982</t>
         </is>
@@ -3459,7 +3489,7 @@
           <t>YAZAWA Aki</t>
         </is>
       </c>
-      <c r="U55" t="inlineStr">
+      <c r="X55" t="inlineStr">
         <is>
           <t>36486</t>
         </is>
@@ -3517,7 +3547,7 @@
           <t>SORRIBES Laia</t>
         </is>
       </c>
-      <c r="U56" t="inlineStr">
+      <c r="X56" t="inlineStr">
         <is>
           <t>68822</t>
         </is>
@@ -3575,7 +3605,7 @@
           <t>VUITTON Emma</t>
         </is>
       </c>
-      <c r="U57" t="inlineStr">
+      <c r="X57" t="inlineStr">
         <is>
           <t>84126</t>
         </is>
@@ -3633,7 +3663,7 @@
           <t>FOX Noemie</t>
         </is>
       </c>
-      <c r="U58" t="inlineStr">
+      <c r="X58" t="inlineStr">
         <is>
           <t>44812</t>
         </is>
@@ -3691,7 +3721,7 @@
           <t>NOVAK Ajda</t>
         </is>
       </c>
-      <c r="U59" t="inlineStr">
+      <c r="X59" t="inlineStr">
         <is>
           <t>39079</t>
         </is>
@@ -3749,7 +3779,7 @@
           <t>DORIA VILARRUBLA Monica</t>
         </is>
       </c>
-      <c r="U60" t="inlineStr">
+      <c r="X60" t="inlineStr">
         <is>
           <t>53051</t>
         </is>
@@ -3807,7 +3837,7 @@
           <t>HOCEVAR Eva Alina</t>
         </is>
       </c>
-      <c r="U61" t="inlineStr">
+      <c r="X61" t="inlineStr">
         <is>
           <t>75533</t>
         </is>
@@ -3865,7 +3895,7 @@
           <t>GALUSKOVA Antonie</t>
         </is>
       </c>
-      <c r="U62" t="inlineStr">
+      <c r="X62" t="inlineStr">
         <is>
           <t>68754</t>
         </is>
@@ -3923,7 +3953,7 @@
           <t>PRIGENT Romane</t>
         </is>
       </c>
-      <c r="U63" t="inlineStr">
+      <c r="X63" t="inlineStr">
         <is>
           <t>71968</t>
         </is>
@@ -3981,7 +4011,7 @@
           <t>VALIKOVA Barbora</t>
         </is>
       </c>
-      <c r="U64" t="inlineStr">
+      <c r="X64" t="inlineStr">
         <is>
           <t>37267</t>
         </is>
@@ -4039,7 +4069,7 @@
           <t>PACIERPNIK Natalia</t>
         </is>
       </c>
-      <c r="U65" t="inlineStr">
+      <c r="X65" t="inlineStr">
         <is>
           <t>35077</t>
         </is>
@@ -4097,7 +4127,7 @@
           <t>FISEROVA Tereza</t>
         </is>
       </c>
-      <c r="U66" t="inlineStr">
+      <c r="X66" t="inlineStr">
         <is>
           <t>42016</t>
         </is>
@@ -4155,7 +4185,7 @@
           <t>WEGMAN Martina</t>
         </is>
       </c>
-      <c r="U67" t="inlineStr">
+      <c r="X67" t="inlineStr">
         <is>
           <t>35345</t>
         </is>
@@ -4213,7 +4243,7 @@
           <t>WOLFFHARDT Viktoria</t>
         </is>
       </c>
-      <c r="U68" t="inlineStr">
+      <c r="X68" t="inlineStr">
         <is>
           <t>35303</t>
         </is>
@@ -4271,7 +4301,7 @@
           <t>ZWOLINSKA Klaudia</t>
         </is>
       </c>
-      <c r="U69" t="inlineStr">
+      <c r="X69" t="inlineStr">
         <is>
           <t>42027</t>
         </is>
@@ -4329,7 +4359,7 @@
           <t>MINTALOVA Eliska</t>
         </is>
       </c>
-      <c r="U70" t="inlineStr">
+      <c r="X70" t="inlineStr">
         <is>
           <t>56169</t>
         </is>
@@ -4387,7 +4417,7 @@
           <t>WOODS Kimberley</t>
         </is>
       </c>
-      <c r="U71" t="inlineStr">
+      <c r="X71" t="inlineStr">
         <is>
           <t>35650</t>
         </is>
@@ -4445,7 +4475,7 @@
           <t>SATILA Ana</t>
         </is>
       </c>
-      <c r="U72" t="inlineStr">
+      <c r="X72" t="inlineStr">
         <is>
           <t>35327</t>
         </is>
@@ -4503,7 +4533,7 @@
           <t>US Viktoriia</t>
         </is>
       </c>
-      <c r="U73" t="inlineStr">
+      <c r="X73" t="inlineStr">
         <is>
           <t>35528</t>
         </is>
@@ -4561,7 +4591,7 @@
           <t>LILIK Elena</t>
         </is>
       </c>
-      <c r="U74" t="inlineStr">
+      <c r="X74" t="inlineStr">
         <is>
           <t>51837</t>
         </is>
@@ -4619,7 +4649,7 @@
           <t>PRIGENT Camille</t>
         </is>
       </c>
-      <c r="U75" t="inlineStr">
+      <c r="X75" t="inlineStr">
         <is>
           <t>41566</t>
         </is>
@@ -4677,7 +4707,7 @@
           <t>CHOURRAUT Maialen</t>
         </is>
       </c>
-      <c r="U76" t="inlineStr">
+      <c r="X76" t="inlineStr">
         <is>
           <t>35787</t>
         </is>
@@ -4735,7 +4765,7 @@
           <t>HORN Stefanie</t>
         </is>
       </c>
-      <c r="U77" t="inlineStr">
+      <c r="X77" t="inlineStr">
         <is>
           <t>38417</t>
         </is>
@@ -4793,7 +4823,7 @@
           <t>FRANKLIN Mallory</t>
         </is>
       </c>
-      <c r="U78" t="inlineStr">
+      <c r="X78" t="inlineStr">
         <is>
           <t>35615</t>
         </is>
@@ -4851,7 +4881,7 @@
           <t>TERCELJ Eva</t>
         </is>
       </c>
-      <c r="U79" t="inlineStr">
+      <c r="X79" t="inlineStr">
         <is>
           <t>36263</t>
         </is>
@@ -4909,7 +4939,7 @@
           <t>KUHNLE Corinna</t>
         </is>
       </c>
-      <c r="U80" t="inlineStr">
+      <c r="X80" t="inlineStr">
         <is>
           <t>35282</t>
         </is>
@@ -4967,7 +4997,7 @@
           <t>FUNK Ricarda</t>
         </is>
       </c>
-      <c r="U81" t="inlineStr">
+      <c r="X81" t="inlineStr">
         <is>
           <t>35122</t>
         </is>
@@ -5025,7 +5055,7 @@
           <t>FOX Jessica</t>
         </is>
       </c>
-      <c r="U82" t="inlineStr">
+      <c r="X82" t="inlineStr">
         <is>
           <t>36526</t>
         </is>
@@ -5083,7 +5113,7 @@
           <t>LIN Chao-Jun</t>
         </is>
       </c>
-      <c r="U83" t="inlineStr">
+      <c r="X83" t="inlineStr">
         <is>
           <t>122610</t>
         </is>
@@ -5141,7 +5171,7 @@
           <t>YU Haijie</t>
         </is>
       </c>
-      <c r="U84" t="inlineStr">
+      <c r="X84" t="inlineStr">
         <is>
           <t>118849</t>
         </is>
@@ -5199,7 +5229,7 @@
           <t>CUNHA Joao</t>
         </is>
       </c>
-      <c r="U85" t="inlineStr">
+      <c r="X85" t="inlineStr">
         <is>
           <t>76853</t>
         </is>
@@ -5257,7 +5287,7 @@
           <t>LACOUR Thibaud</t>
         </is>
       </c>
-      <c r="U86" t="inlineStr">
+      <c r="X86" t="inlineStr">
         <is>
           <t>120074</t>
         </is>
@@ -5315,7 +5345,7 @@
           <t>JACOB Lucas</t>
         </is>
       </c>
-      <c r="U87" t="inlineStr">
+      <c r="X87" t="inlineStr">
         <is>
           <t>106067</t>
         </is>
@@ -5373,7 +5403,7 @@
           <t>REINOSO Antonio</t>
         </is>
       </c>
-      <c r="U88" t="inlineStr">
+      <c r="X88" t="inlineStr">
         <is>
           <t>70420</t>
         </is>
@@ -5431,7 +5461,7 @@
           <t>TRIPANO Manuel</t>
         </is>
       </c>
-      <c r="U89" t="inlineStr">
+      <c r="X89" t="inlineStr">
         <is>
           <t>93235</t>
         </is>
@@ -5489,7 +5519,7 @@
           <t>HUANG Liman</t>
         </is>
       </c>
-      <c r="U90" t="inlineStr">
+      <c r="X90" t="inlineStr">
         <is>
           <t>118848</t>
         </is>
@@ -5547,7 +5577,7 @@
           <t>UKALOVIC Thomas</t>
         </is>
       </c>
-      <c r="U91" t="inlineStr">
+      <c r="X91" t="inlineStr">
         <is>
           <t>93708</t>
         </is>
@@ -5605,7 +5635,7 @@
           <t>AIT KADDOUR Nour</t>
         </is>
       </c>
-      <c r="U92" t="inlineStr">
+      <c r="X92" t="inlineStr">
         <is>
           <t>96649</t>
         </is>
@@ -5663,7 +5693,7 @@
           <t>HENNIN Victor</t>
         </is>
       </c>
-      <c r="U93" t="inlineStr">
+      <c r="X93" t="inlineStr">
         <is>
           <t>68819</t>
         </is>
@@ -5721,7 +5751,7 @@
           <t>RIVARD Mael</t>
         </is>
       </c>
-      <c r="U94" t="inlineStr">
+      <c r="X94" t="inlineStr">
         <is>
           <t>75978</t>
         </is>
@@ -5779,7 +5809,7 @@
           <t>SOVKO Serhii</t>
         </is>
       </c>
-      <c r="U95" t="inlineStr">
+      <c r="X95" t="inlineStr">
         <is>
           <t>94235</t>
         </is>
@@ -5837,7 +5867,7 @@
           <t>CORTEZ Geronimo</t>
         </is>
       </c>
-      <c r="U96" t="inlineStr">
+      <c r="X96" t="inlineStr">
         <is>
           <t>51835</t>
         </is>
@@ -5895,7 +5925,7 @@
           <t>BALDONI Alex</t>
         </is>
       </c>
-      <c r="U97" t="inlineStr">
+      <c r="X97" t="inlineStr">
         <is>
           <t>94528</t>
         </is>
@@ -5953,7 +5983,7 @@
           <t>MACUS Ondrej</t>
         </is>
       </c>
-      <c r="U98" t="inlineStr">
+      <c r="X98" t="inlineStr">
         <is>
           <t>94095</t>
         </is>
@@ -6011,7 +6041,7 @@
           <t>DICKSON Jonny</t>
         </is>
       </c>
-      <c r="U99" t="inlineStr">
+      <c r="X99" t="inlineStr">
         <is>
           <t>75973</t>
         </is>
@@ -6069,7 +6099,7 @@
           <t>BOYD Trevor</t>
         </is>
       </c>
-      <c r="U100" t="inlineStr">
+      <c r="X100" t="inlineStr">
         <is>
           <t>71799</t>
         </is>
@@ -6127,7 +6157,7 @@
           <t>SHERMAN Jordan</t>
         </is>
       </c>
-      <c r="U101" t="inlineStr">
+      <c r="X101" t="inlineStr">
         <is>
           <t>51905</t>
         </is>
@@ -6185,7 +6215,7 @@
           <t>HAYLETT Ben</t>
         </is>
       </c>
-      <c r="U102" t="inlineStr">
+      <c r="X102" t="inlineStr">
         <is>
           <t>69122</t>
         </is>
@@ -6243,7 +6273,7 @@
           <t>FRIEDENSON Kaelin</t>
         </is>
       </c>
-      <c r="U103" t="inlineStr">
+      <c r="X103" t="inlineStr">
         <is>
           <t>87397</t>
         </is>
@@ -6301,7 +6331,7 @@
           <t>CURTIS Samuel</t>
         </is>
       </c>
-      <c r="U104" t="inlineStr">
+      <c r="X104" t="inlineStr">
         <is>
           <t>36683</t>
         </is>
@@ -6359,7 +6389,7 @@
           <t>RACZ Koppany</t>
         </is>
       </c>
-      <c r="U105" t="inlineStr">
+      <c r="X105" t="inlineStr">
         <is>
           <t>69570</t>
         </is>
@@ -6417,7 +6447,7 @@
           <t>AUBERTIN Maxime</t>
         </is>
       </c>
-      <c r="U106" t="inlineStr">
+      <c r="X106" t="inlineStr">
         <is>
           <t>104390</t>
         </is>
@@ -6475,7 +6505,7 @@
           <t>MCCREERY Alistair</t>
         </is>
       </c>
-      <c r="U107" t="inlineStr">
+      <c r="X107" t="inlineStr">
         <is>
           <t>60125</t>
         </is>
@@ -6533,7 +6563,7 @@
           <t>VALANT Ulan</t>
         </is>
       </c>
-      <c r="U108" t="inlineStr">
+      <c r="X108" t="inlineStr">
         <is>
           <t>83908</t>
         </is>
@@ -6591,7 +6621,7 @@
           <t>TANAKA Yuuki</t>
         </is>
       </c>
-      <c r="U109" t="inlineStr">
+      <c r="X109" t="inlineStr">
         <is>
           <t>75422</t>
         </is>
@@ -6649,7 +6679,7 @@
           <t>ROSSI Lucas</t>
         </is>
       </c>
-      <c r="U110" t="inlineStr">
+      <c r="X110" t="inlineStr">
         <is>
           <t>36925</t>
         </is>
@@ -6707,7 +6737,7 @@
           <t>MUTTON Zack</t>
         </is>
       </c>
-      <c r="U111" t="inlineStr">
+      <c r="X111" t="inlineStr">
         <is>
           <t>51827</t>
         </is>
@@ -6765,7 +6795,7 @@
           <t>WAHLEN Fredrik</t>
         </is>
       </c>
-      <c r="U112" t="inlineStr">
+      <c r="X112" t="inlineStr">
         <is>
           <t>35102</t>
         </is>
@@ -6823,7 +6853,7 @@
           <t>MUTO Yusuke</t>
         </is>
       </c>
-      <c r="U113" t="inlineStr">
+      <c r="X113" t="inlineStr">
         <is>
           <t>71820</t>
         </is>
@@ -6881,7 +6911,7 @@
           <t>HENDRICK Noel</t>
         </is>
       </c>
-      <c r="U114" t="inlineStr">
+      <c r="X114" t="inlineStr">
         <is>
           <t>43003</t>
         </is>
@@ -6939,7 +6969,7 @@
           <t>DE COSTER Gabriel</t>
         </is>
       </c>
-      <c r="U115" t="inlineStr">
+      <c r="X115" t="inlineStr">
         <is>
           <t>68818</t>
         </is>
@@ -6997,7 +7027,7 @@
           <t>BREMER Tim</t>
         </is>
       </c>
-      <c r="U116" t="inlineStr">
+      <c r="X116" t="inlineStr">
         <is>
           <t>84001</t>
         </is>
@@ -7055,7 +7085,7 @@
           <t>OCHOA Manuel</t>
         </is>
       </c>
-      <c r="U117" t="inlineStr">
+      <c r="X117" t="inlineStr">
         <is>
           <t>69081</t>
         </is>
@@ -7113,7 +7143,7 @@
           <t>GONSENICA Adam</t>
         </is>
       </c>
-      <c r="U118" t="inlineStr">
+      <c r="X118" t="inlineStr">
         <is>
           <t>55165</t>
         </is>
@@ -7171,7 +7201,7 @@
           <t>HOLMER Erik</t>
         </is>
       </c>
-      <c r="U119" t="inlineStr">
+      <c r="X119" t="inlineStr">
         <is>
           <t>35104</t>
         </is>
@@ -7229,7 +7259,7 @@
           <t>BRZEZINSKI Jakub</t>
         </is>
       </c>
-      <c r="U120" t="inlineStr">
+      <c r="X120" t="inlineStr">
         <is>
           <t>43977</t>
         </is>
@@ -7287,7 +7317,7 @@
           <t>TRAVE Miquel</t>
         </is>
       </c>
-      <c r="U121" t="inlineStr">
+      <c r="X121" t="inlineStr">
         <is>
           <t>68998</t>
         </is>
@@ -7345,7 +7375,7 @@
           <t>POPE Benjamin</t>
         </is>
       </c>
-      <c r="U122" t="inlineStr">
+      <c r="X122" t="inlineStr">
         <is>
           <t>51753</t>
         </is>
@@ -7403,7 +7433,7 @@
           <t>QUAN Xin</t>
         </is>
       </c>
-      <c r="U123" t="inlineStr">
+      <c r="X123" t="inlineStr">
         <is>
           <t>62343</t>
         </is>
@@ -7461,7 +7491,7 @@
           <t>CASTRYCK Titouan</t>
         </is>
       </c>
-      <c r="U124" t="inlineStr">
+      <c r="X124" t="inlineStr">
         <is>
           <t>88701</t>
         </is>
@@ -7519,7 +7549,7 @@
           <t>ANDERSON Timothy</t>
         </is>
       </c>
-      <c r="U125" t="inlineStr">
+      <c r="X125" t="inlineStr">
         <is>
           <t>38432</t>
         </is>
@@ -7577,7 +7607,7 @@
           <t>GONCALVES Pedro</t>
         </is>
       </c>
-      <c r="U126" t="inlineStr">
+      <c r="X126" t="inlineStr">
         <is>
           <t>38017</t>
         </is>
@@ -7635,7 +7665,7 @@
           <t>CHIARELLO Gelindo</t>
         </is>
       </c>
-      <c r="U127" t="inlineStr">
+      <c r="X127" t="inlineStr">
         <is>
           <t>39956</t>
         </is>
@@ -7693,7 +7723,7 @@
           <t>ADACHI Kazuya</t>
         </is>
       </c>
-      <c r="U128" t="inlineStr">
+      <c r="X128" t="inlineStr">
         <is>
           <t>36646</t>
         </is>
@@ -7751,7 +7781,7 @@
           <t>IVALDI Zeno</t>
         </is>
       </c>
-      <c r="U129" t="inlineStr">
+      <c r="X129" t="inlineStr">
         <is>
           <t>35480</t>
         </is>
@@ -7809,7 +7839,7 @@
           <t>OHRSTROM Isak</t>
         </is>
       </c>
-      <c r="U130" t="inlineStr">
+      <c r="X130" t="inlineStr">
         <is>
           <t>35101</t>
         </is>
@@ -7867,7 +7897,7 @@
           <t>BUTCHER Finn</t>
         </is>
       </c>
-      <c r="U131" t="inlineStr">
+      <c r="X131" t="inlineStr">
         <is>
           <t>36663</t>
         </is>
@@ -7925,7 +7955,7 @@
           <t>GILBERT Callum</t>
         </is>
       </c>
-      <c r="U132" t="inlineStr">
+      <c r="X132" t="inlineStr">
         <is>
           <t>42090</t>
         </is>
@@ -7983,7 +8013,7 @@
           <t>POPIELA Dariusz</t>
         </is>
       </c>
-      <c r="U133" t="inlineStr">
+      <c r="X133" t="inlineStr">
         <is>
           <t>35096</t>
         </is>
@@ -8041,7 +8071,7 @@
           <t>HALCIN Martin</t>
         </is>
       </c>
-      <c r="U134" t="inlineStr">
+      <c r="X134" t="inlineStr">
         <is>
           <t>35355</t>
         </is>
@@ -8099,7 +8129,7 @@
           <t>LEITNER Mario</t>
         </is>
       </c>
-      <c r="U135" t="inlineStr">
+      <c r="X135" t="inlineStr">
         <is>
           <t>35546</t>
         </is>
@@ -8157,7 +8187,7 @@
           <t>BEDA Marcello</t>
         </is>
       </c>
-      <c r="U136" t="inlineStr">
+      <c r="X136" t="inlineStr">
         <is>
           <t>39899</t>
         </is>
@@ -8215,7 +8245,7 @@
           <t>QUEMENEUR Malo</t>
         </is>
       </c>
-      <c r="U137" t="inlineStr">
+      <c r="X137" t="inlineStr">
         <is>
           <t>60403</t>
         </is>
@@ -8273,7 +8303,7 @@
           <t>WERRO Lukas</t>
         </is>
       </c>
-      <c r="U138" t="inlineStr">
+      <c r="X138" t="inlineStr">
         <is>
           <t>35347</t>
         </is>
@@ -8331,7 +8361,7 @@
           <t>HEGGE Noah</t>
         </is>
       </c>
-      <c r="U139" t="inlineStr">
+      <c r="X139" t="inlineStr">
         <is>
           <t>71837</t>
         </is>
@@ -8389,7 +8419,7 @@
           <t>PASIUT Michal</t>
         </is>
       </c>
-      <c r="U140" t="inlineStr">
+      <c r="X140" t="inlineStr">
         <is>
           <t>35095</t>
         </is>
@@ -8447,7 +8477,7 @@
           <t>HENGST Stefan</t>
         </is>
       </c>
-      <c r="U141" t="inlineStr">
+      <c r="X141" t="inlineStr">
         <is>
           <t>39061</t>
         </is>
@@ -8505,7 +8535,7 @@
           <t>SRABOTNIK Martin</t>
         </is>
       </c>
-      <c r="U142" t="inlineStr">
+      <c r="X142" t="inlineStr">
         <is>
           <t>39080</t>
         </is>
@@ -8563,7 +8593,7 @@
           <t>OSCHMAUTZ Felix</t>
         </is>
       </c>
-      <c r="U143" t="inlineStr">
+      <c r="X143" t="inlineStr">
         <is>
           <t>51856</t>
         </is>
@@ -8621,7 +8651,7 @@
           <t>TUNKA Ondrej</t>
         </is>
       </c>
-      <c r="U144" t="inlineStr">
+      <c r="X144" t="inlineStr">
         <is>
           <t>35947</t>
         </is>
@@ -8679,7 +8709,7 @@
           <t>CRESPO Joan</t>
         </is>
       </c>
-      <c r="U145" t="inlineStr">
+      <c r="X145" t="inlineStr">
         <is>
           <t>35749</t>
         </is>
@@ -8737,7 +8767,7 @@
           <t>DELFOUR Lucien</t>
         </is>
       </c>
-      <c r="U146" t="inlineStr">
+      <c r="X146" t="inlineStr">
         <is>
           <t>36537</t>
         </is>
@@ -8795,7 +8825,7 @@
           <t>DOUGOUD Martin</t>
         </is>
       </c>
-      <c r="U147" t="inlineStr">
+      <c r="X147" t="inlineStr">
         <is>
           <t>35426</t>
         </is>
@@ -8853,7 +8883,7 @@
           <t>CLARKE Joseph</t>
         </is>
       </c>
-      <c r="U148" t="inlineStr">
+      <c r="X148" t="inlineStr">
         <is>
           <t>35654</t>
         </is>
@@ -8911,7 +8941,7 @@
           <t>NEVEU Boris</t>
         </is>
       </c>
-      <c r="U149" t="inlineStr">
+      <c r="X149" t="inlineStr">
         <is>
           <t>35396</t>
         </is>
@@ -8969,7 +8999,7 @@
           <t>DE GENNARO Giovanni</t>
         </is>
       </c>
-      <c r="U150" t="inlineStr">
+      <c r="X150" t="inlineStr">
         <is>
           <t>35244</t>
         </is>
@@ -9027,7 +9057,7 @@
           <t>KAUZER Peter</t>
         </is>
       </c>
-      <c r="U151" t="inlineStr">
+      <c r="X151" t="inlineStr">
         <is>
           <t>35589</t>
         </is>
@@ -9085,7 +9115,7 @@
           <t>PRSKAVEC Jiri</t>
         </is>
       </c>
-      <c r="U152" t="inlineStr">
+      <c r="X152" t="inlineStr">
         <is>
           <t>35033</t>
         </is>
@@ -9143,7 +9173,7 @@
           <t>PRINDIS Vit</t>
         </is>
       </c>
-      <c r="U153" t="inlineStr">
+      <c r="X153" t="inlineStr">
         <is>
           <t>35065</t>
         </is>
@@ -9201,7 +9231,7 @@
           <t>CHOU Chih-Chin</t>
         </is>
       </c>
-      <c r="U154" t="inlineStr">
+      <c r="X154" t="inlineStr">
         <is>
           <t>68975</t>
         </is>
@@ -9259,7 +9289,7 @@
           <t>PISTONI Lucia</t>
         </is>
       </c>
-      <c r="U155" t="inlineStr">
+      <c r="X155" t="inlineStr">
         <is>
           <t>104430</t>
         </is>
@@ -9317,7 +9347,7 @@
           <t>SOMMERNES Iris</t>
         </is>
       </c>
-      <c r="U156" t="inlineStr">
+      <c r="X156" t="inlineStr">
         <is>
           <t>90378</t>
         </is>
@@ -9375,7 +9405,7 @@
           <t>ZOU Xiaolin</t>
         </is>
       </c>
-      <c r="U157" t="inlineStr">
+      <c r="X157" t="inlineStr">
         <is>
           <t>118854</t>
         </is>
@@ -9433,7 +9463,7 @@
           <t>SPICER Phoebe</t>
         </is>
       </c>
-      <c r="U158" t="inlineStr">
+      <c r="X158" t="inlineStr">
         <is>
           <t>75827</t>
         </is>
@@ -9491,7 +9521,7 @@
           <t>JODAR Celia</t>
         </is>
       </c>
-      <c r="U159" t="inlineStr">
+      <c r="X159" t="inlineStr">
         <is>
           <t>36936</t>
         </is>
@@ -9549,7 +9579,7 @@
           <t>RAZEGHIAN Roxana</t>
         </is>
       </c>
-      <c r="U160" t="inlineStr">
+      <c r="X160" t="inlineStr">
         <is>
           <t>63124</t>
         </is>
@@ -9607,7 +9637,7 @@
           <t>RIQUELME Nadia</t>
         </is>
       </c>
-      <c r="U161" t="inlineStr">
+      <c r="X161" t="inlineStr">
         <is>
           <t>41626</t>
         </is>
@@ -9665,7 +9695,7 @@
           <t>CASSINI Maria Luz</t>
         </is>
       </c>
-      <c r="U162" t="inlineStr">
+      <c r="X162" t="inlineStr">
         <is>
           <t>41627</t>
         </is>
@@ -9723,7 +9753,7 @@
           <t>REINOSO Sofia</t>
         </is>
       </c>
-      <c r="U163" t="inlineStr">
+      <c r="X163" t="inlineStr">
         <is>
           <t>45745</t>
         </is>
@@ -9781,7 +9811,7 @@
           <t>BRZESKA Dominika</t>
         </is>
       </c>
-      <c r="U164" t="inlineStr">
+      <c r="X164" t="inlineStr">
         <is>
           <t>93913</t>
         </is>
@@ -9839,7 +9869,7 @@
           <t>MISHIMA Ren</t>
         </is>
       </c>
-      <c r="U165" t="inlineStr">
+      <c r="X165" t="inlineStr">
         <is>
           <t>37757</t>
         </is>
@@ -9897,7 +9927,7 @@
           <t>ITO Kurumi</t>
         </is>
       </c>
-      <c r="U166" t="inlineStr">
+      <c r="X166" t="inlineStr">
         <is>
           <t>83683</t>
         </is>
@@ -9955,7 +9985,7 @@
           <t>GLEJTEKOVA Simona</t>
         </is>
       </c>
-      <c r="U167" t="inlineStr">
+      <c r="X167" t="inlineStr">
         <is>
           <t>55166</t>
         </is>
@@ -10013,7 +10043,7 @@
           <t>COLLIN Georgina</t>
         </is>
       </c>
-      <c r="U168" t="inlineStr">
+      <c r="X168" t="inlineStr">
         <is>
           <t>60108</t>
         </is>
@@ -10071,7 +10101,7 @@
           <t>BALDONI Lea</t>
         </is>
       </c>
-      <c r="U169" t="inlineStr">
+      <c r="X169" t="inlineStr">
         <is>
           <t>94529</t>
         </is>
@@ -10129,7 +10159,7 @@
           <t>KRIESINGER Janina</t>
         </is>
       </c>
-      <c r="U170" t="inlineStr">
+      <c r="X170" t="inlineStr">
         <is>
           <t>93682</t>
         </is>
@@ -10187,7 +10217,7 @@
           <t>APEL Emily</t>
         </is>
       </c>
-      <c r="U171" t="inlineStr">
+      <c r="X171" t="inlineStr">
         <is>
           <t>83788</t>
         </is>
@@ -10245,7 +10275,7 @@
           <t>CUCHI Julia</t>
         </is>
       </c>
-      <c r="U172" t="inlineStr">
+      <c r="X172" t="inlineStr">
         <is>
           <t>35764</t>
         </is>
@@ -10303,7 +10333,7 @@
           <t>BETTERIDGE Lois</t>
         </is>
       </c>
-      <c r="U173" t="inlineStr">
+      <c r="X173" t="inlineStr">
         <is>
           <t>60078</t>
         </is>
@@ -10361,7 +10391,7 @@
           <t>MAHEU Florence</t>
         </is>
       </c>
-      <c r="U174" t="inlineStr">
+      <c r="X174" t="inlineStr">
         <is>
           <t>36416</t>
         </is>
@@ -10419,7 +10449,7 @@
           <t>PELLICER CHICA Laura</t>
         </is>
       </c>
-      <c r="U175" t="inlineStr">
+      <c r="X175" t="inlineStr">
         <is>
           <t>43129</t>
         </is>
@@ -10477,7 +10507,7 @@
           <t>WILLIAMS Courtney</t>
         </is>
       </c>
-      <c r="U176" t="inlineStr">
+      <c r="X176" t="inlineStr">
         <is>
           <t>68771</t>
         </is>
@@ -10535,7 +10565,7 @@
           <t>LEENDERS Claudia</t>
         </is>
       </c>
-      <c r="U177" t="inlineStr">
+      <c r="X177" t="inlineStr">
         <is>
           <t>35331</t>
         </is>
@@ -10593,7 +10623,7 @@
           <t>YAN Jiahua</t>
         </is>
       </c>
-      <c r="U178" t="inlineStr">
+      <c r="X178" t="inlineStr">
         <is>
           <t>43545</t>
         </is>
@@ -10651,7 +10681,7 @@
           <t>SRIBAR Ria</t>
         </is>
       </c>
-      <c r="U179" t="inlineStr">
+      <c r="X179" t="inlineStr">
         <is>
           <t>75645</t>
         </is>
@@ -10709,7 +10739,7 @@
           <t>THOMAS Hannah</t>
         </is>
       </c>
-      <c r="U180" t="inlineStr">
+      <c r="X180" t="inlineStr">
         <is>
           <t>85758</t>
         </is>
@@ -10767,7 +10797,7 @@
           <t>MARX Alena</t>
         </is>
       </c>
-      <c r="U181" t="inlineStr">
+      <c r="X181" t="inlineStr">
         <is>
           <t>68844</t>
         </is>
@@ -10825,7 +10855,7 @@
           <t>LI Tong</t>
         </is>
       </c>
-      <c r="U182" t="inlineStr">
+      <c r="X182" t="inlineStr">
         <is>
           <t>52023</t>
         </is>
@@ -10883,7 +10913,7 @@
           <t>BERTONCELLI Marta</t>
         </is>
       </c>
-      <c r="U183" t="inlineStr">
+      <c r="X183" t="inlineStr">
         <is>
           <t>71982</t>
         </is>
@@ -10941,7 +10971,7 @@
           <t>YAZAWA Aki</t>
         </is>
       </c>
-      <c r="U184" t="inlineStr">
+      <c r="X184" t="inlineStr">
         <is>
           <t>36486</t>
         </is>
@@ -10999,7 +11029,7 @@
           <t>FOX Noemie</t>
         </is>
       </c>
-      <c r="U185" t="inlineStr">
+      <c r="X185" t="inlineStr">
         <is>
           <t>44812</t>
         </is>
@@ -11057,7 +11087,7 @@
           <t>NOVAK Ajda</t>
         </is>
       </c>
-      <c r="U186" t="inlineStr">
+      <c r="X186" t="inlineStr">
         <is>
           <t>39079</t>
         </is>
@@ -11115,7 +11145,7 @@
           <t>HOCEVAR Eva Alina</t>
         </is>
       </c>
-      <c r="U187" t="inlineStr">
+      <c r="X187" t="inlineStr">
         <is>
           <t>75533</t>
         </is>
@@ -11173,7 +11203,7 @@
           <t>VALIKOVA Barbora</t>
         </is>
       </c>
-      <c r="U188" t="inlineStr">
+      <c r="X188" t="inlineStr">
         <is>
           <t>37267</t>
         </is>
@@ -11231,7 +11261,7 @@
           <t>PACIERPNIK Natalia</t>
         </is>
       </c>
-      <c r="U189" t="inlineStr">
+      <c r="X189" t="inlineStr">
         <is>
           <t>35077</t>
         </is>
@@ -11289,7 +11319,7 @@
           <t>FISEROVA Tereza</t>
         </is>
       </c>
-      <c r="U190" t="inlineStr">
+      <c r="X190" t="inlineStr">
         <is>
           <t>42016</t>
         </is>
@@ -11347,7 +11377,7 @@
           <t>WEGMAN Martina</t>
         </is>
       </c>
-      <c r="U191" t="inlineStr">
+      <c r="X191" t="inlineStr">
         <is>
           <t>35345</t>
         </is>
@@ -11405,7 +11435,7 @@
           <t>MINTALOVA Eliska</t>
         </is>
       </c>
-      <c r="U192" t="inlineStr">
+      <c r="X192" t="inlineStr">
         <is>
           <t>56169</t>
         </is>
@@ -11463,7 +11493,7 @@
           <t>SATILA Ana</t>
         </is>
       </c>
-      <c r="U193" t="inlineStr">
+      <c r="X193" t="inlineStr">
         <is>
           <t>35327</t>
         </is>
@@ -11521,7 +11551,7 @@
           <t>LILIK Elena</t>
         </is>
       </c>
-      <c r="U194" t="inlineStr">
+      <c r="X194" t="inlineStr">
         <is>
           <t>51837</t>
         </is>
@@ -11579,7 +11609,7 @@
           <t>LIN Chao-Jun</t>
         </is>
       </c>
-      <c r="U195" t="inlineStr">
+      <c r="X195" t="inlineStr">
         <is>
           <t>122610</t>
         </is>
@@ -11637,7 +11667,7 @@
           <t>YU Haijie</t>
         </is>
       </c>
-      <c r="U196" t="inlineStr">
+      <c r="X196" t="inlineStr">
         <is>
           <t>118849</t>
         </is>
@@ -11695,7 +11725,7 @@
           <t>CUNHA Joao</t>
         </is>
       </c>
-      <c r="U197" t="inlineStr">
+      <c r="X197" t="inlineStr">
         <is>
           <t>76853</t>
         </is>
@@ -11753,7 +11783,7 @@
           <t>LACOUR Thibaud</t>
         </is>
       </c>
-      <c r="U198" t="inlineStr">
+      <c r="X198" t="inlineStr">
         <is>
           <t>120074</t>
         </is>
@@ -11811,7 +11841,7 @@
           <t>JACOB Lucas</t>
         </is>
       </c>
-      <c r="U199" t="inlineStr">
+      <c r="X199" t="inlineStr">
         <is>
           <t>106067</t>
         </is>
@@ -11869,7 +11899,7 @@
           <t>REINOSO Antonio</t>
         </is>
       </c>
-      <c r="U200" t="inlineStr">
+      <c r="X200" t="inlineStr">
         <is>
           <t>70420</t>
         </is>
@@ -11927,7 +11957,7 @@
           <t>TRIPANO Manuel</t>
         </is>
       </c>
-      <c r="U201" t="inlineStr">
+      <c r="X201" t="inlineStr">
         <is>
           <t>93235</t>
         </is>
@@ -11985,7 +12015,7 @@
           <t>HUANG Liman</t>
         </is>
       </c>
-      <c r="U202" t="inlineStr">
+      <c r="X202" t="inlineStr">
         <is>
           <t>118848</t>
         </is>
@@ -12043,7 +12073,7 @@
           <t>UKALOVIC Thomas</t>
         </is>
       </c>
-      <c r="U203" t="inlineStr">
+      <c r="X203" t="inlineStr">
         <is>
           <t>93708</t>
         </is>
@@ -12101,7 +12131,7 @@
           <t>AIT KADDOUR Nour</t>
         </is>
       </c>
-      <c r="U204" t="inlineStr">
+      <c r="X204" t="inlineStr">
         <is>
           <t>96649</t>
         </is>
@@ -12159,7 +12189,7 @@
           <t>HENNIN Victor</t>
         </is>
       </c>
-      <c r="U205" t="inlineStr">
+      <c r="X205" t="inlineStr">
         <is>
           <t>68819</t>
         </is>
@@ -12217,7 +12247,7 @@
           <t>RIVARD Mael</t>
         </is>
       </c>
-      <c r="U206" t="inlineStr">
+      <c r="X206" t="inlineStr">
         <is>
           <t>75978</t>
         </is>
@@ -12275,7 +12305,7 @@
           <t>SOVKO Serhii</t>
         </is>
       </c>
-      <c r="U207" t="inlineStr">
+      <c r="X207" t="inlineStr">
         <is>
           <t>94235</t>
         </is>
@@ -12333,7 +12363,7 @@
           <t>CORTEZ Geronimo</t>
         </is>
       </c>
-      <c r="U208" t="inlineStr">
+      <c r="X208" t="inlineStr">
         <is>
           <t>51835</t>
         </is>
@@ -12391,7 +12421,7 @@
           <t>BALDONI Alex</t>
         </is>
       </c>
-      <c r="U209" t="inlineStr">
+      <c r="X209" t="inlineStr">
         <is>
           <t>94528</t>
         </is>
@@ -12449,7 +12479,7 @@
           <t>MACUS Ondrej</t>
         </is>
       </c>
-      <c r="U210" t="inlineStr">
+      <c r="X210" t="inlineStr">
         <is>
           <t>94095</t>
         </is>
@@ -12507,7 +12537,7 @@
           <t>DICKSON Jonny</t>
         </is>
       </c>
-      <c r="U211" t="inlineStr">
+      <c r="X211" t="inlineStr">
         <is>
           <t>75973</t>
         </is>
@@ -12565,7 +12595,7 @@
           <t>BOYD Trevor</t>
         </is>
       </c>
-      <c r="U212" t="inlineStr">
+      <c r="X212" t="inlineStr">
         <is>
           <t>71799</t>
         </is>
@@ -12623,7 +12653,7 @@
           <t>SHERMAN Jordan</t>
         </is>
       </c>
-      <c r="U213" t="inlineStr">
+      <c r="X213" t="inlineStr">
         <is>
           <t>51905</t>
         </is>
@@ -12681,7 +12711,7 @@
           <t>HAYLETT Ben</t>
         </is>
       </c>
-      <c r="U214" t="inlineStr">
+      <c r="X214" t="inlineStr">
         <is>
           <t>69122</t>
         </is>
@@ -12739,7 +12769,7 @@
           <t>FRIEDENSON Kaelin</t>
         </is>
       </c>
-      <c r="U215" t="inlineStr">
+      <c r="X215" t="inlineStr">
         <is>
           <t>87397</t>
         </is>
@@ -12797,7 +12827,7 @@
           <t>CURTIS Samuel</t>
         </is>
       </c>
-      <c r="U216" t="inlineStr">
+      <c r="X216" t="inlineStr">
         <is>
           <t>36683</t>
         </is>
@@ -12855,7 +12885,7 @@
           <t>RACZ Koppany</t>
         </is>
       </c>
-      <c r="U217" t="inlineStr">
+      <c r="X217" t="inlineStr">
         <is>
           <t>69570</t>
         </is>
@@ -12913,7 +12943,7 @@
           <t>AUBERTIN Maxime</t>
         </is>
       </c>
-      <c r="U218" t="inlineStr">
+      <c r="X218" t="inlineStr">
         <is>
           <t>104390</t>
         </is>
@@ -12971,7 +13001,7 @@
           <t>MCCREERY Alistair</t>
         </is>
       </c>
-      <c r="U219" t="inlineStr">
+      <c r="X219" t="inlineStr">
         <is>
           <t>60125</t>
         </is>
@@ -13029,7 +13059,7 @@
           <t>VALANT Ulan</t>
         </is>
       </c>
-      <c r="U220" t="inlineStr">
+      <c r="X220" t="inlineStr">
         <is>
           <t>83908</t>
         </is>
@@ -13087,7 +13117,7 @@
           <t>TANAKA Yuuki</t>
         </is>
       </c>
-      <c r="U221" t="inlineStr">
+      <c r="X221" t="inlineStr">
         <is>
           <t>75422</t>
         </is>
@@ -13145,7 +13175,7 @@
           <t>ROSSI Lucas</t>
         </is>
       </c>
-      <c r="U222" t="inlineStr">
+      <c r="X222" t="inlineStr">
         <is>
           <t>36925</t>
         </is>
@@ -13203,7 +13233,7 @@
           <t>MUTTON Zack</t>
         </is>
       </c>
-      <c r="U223" t="inlineStr">
+      <c r="X223" t="inlineStr">
         <is>
           <t>51827</t>
         </is>
@@ -13261,7 +13291,7 @@
           <t>WAHLEN Fredrik</t>
         </is>
       </c>
-      <c r="U224" t="inlineStr">
+      <c r="X224" t="inlineStr">
         <is>
           <t>35102</t>
         </is>
@@ -13319,7 +13349,7 @@
           <t>DE COSTER Gabriel</t>
         </is>
       </c>
-      <c r="U225" t="inlineStr">
+      <c r="X225" t="inlineStr">
         <is>
           <t>68818</t>
         </is>
@@ -13377,7 +13407,7 @@
           <t>GONSENICA Adam</t>
         </is>
       </c>
-      <c r="U226" t="inlineStr">
+      <c r="X226" t="inlineStr">
         <is>
           <t>55165</t>
         </is>
@@ -13435,7 +13465,7 @@
           <t>HOLMER Erik</t>
         </is>
       </c>
-      <c r="U227" t="inlineStr">
+      <c r="X227" t="inlineStr">
         <is>
           <t>35104</t>
         </is>
@@ -13493,7 +13523,7 @@
           <t>POPE Benjamin</t>
         </is>
       </c>
-      <c r="U228" t="inlineStr">
+      <c r="X228" t="inlineStr">
         <is>
           <t>51753</t>
         </is>
@@ -13551,7 +13581,7 @@
           <t>IVALDI Zeno</t>
         </is>
       </c>
-      <c r="U229" t="inlineStr">
+      <c r="X229" t="inlineStr">
         <is>
           <t>35480</t>
         </is>
@@ -13609,7 +13639,7 @@
           <t>GILBERT Callum</t>
         </is>
       </c>
-      <c r="U230" t="inlineStr">
+      <c r="X230" t="inlineStr">
         <is>
           <t>42090</t>
         </is>
@@ -13667,7 +13697,7 @@
           <t>POPIELA Dariusz</t>
         </is>
       </c>
-      <c r="U231" t="inlineStr">
+      <c r="X231" t="inlineStr">
         <is>
           <t>35096</t>
         </is>
@@ -13725,7 +13755,7 @@
           <t>HALCIN Martin</t>
         </is>
       </c>
-      <c r="U232" t="inlineStr">
+      <c r="X232" t="inlineStr">
         <is>
           <t>35355</t>
         </is>
@@ -13783,7 +13813,7 @@
           <t>BEDA Marcello</t>
         </is>
       </c>
-      <c r="U233" t="inlineStr">
+      <c r="X233" t="inlineStr">
         <is>
           <t>39899</t>
         </is>
@@ -13841,7 +13871,7 @@
           <t>SRABOTNIK Martin</t>
         </is>
       </c>
-      <c r="U234" t="inlineStr">
+      <c r="X234" t="inlineStr">
         <is>
           <t>39080</t>
         </is>
@@ -13899,7 +13929,7 @@
           <t>TUNKA Ondrej</t>
         </is>
       </c>
-      <c r="U235" t="inlineStr">
+      <c r="X235" t="inlineStr">
         <is>
           <t>35947</t>
         </is>
@@ -14159,7 +14189,7 @@
           <t>CEJAS Macarena</t>
         </is>
       </c>
-      <c r="U240" t="inlineStr">
+      <c r="X240" t="inlineStr">
         <is>
           <t>93234</t>
         </is>
@@ -14217,7 +14247,7 @@
           <t>CHOU Chih-Chin</t>
         </is>
       </c>
-      <c r="U241" t="inlineStr">
+      <c r="X241" t="inlineStr">
         <is>
           <t>68975</t>
         </is>
@@ -14275,7 +14305,7 @@
           <t>OKAZAKI Haruka</t>
         </is>
       </c>
-      <c r="U242" t="inlineStr">
+      <c r="X242" t="inlineStr">
         <is>
           <t>42265</t>
         </is>
@@ -14333,7 +14363,7 @@
           <t>CHEN Wei-Han</t>
         </is>
       </c>
-      <c r="U243" t="inlineStr">
+      <c r="X243" t="inlineStr">
         <is>
           <t>61630</t>
         </is>
@@ -14391,7 +14421,7 @@
           <t>HUANG Yanzhi</t>
         </is>
       </c>
-      <c r="U244" t="inlineStr">
+      <c r="X244" t="inlineStr">
         <is>
           <t>106165</t>
         </is>
@@ -14449,7 +14479,7 @@
           <t>YANG Liu</t>
         </is>
       </c>
-      <c r="U245" t="inlineStr">
+      <c r="X245" t="inlineStr">
         <is>
           <t>87649</t>
         </is>
@@ -14507,7 +14537,7 @@
           <t>MISHIMA Ren</t>
         </is>
       </c>
-      <c r="U246" t="inlineStr">
+      <c r="X246" t="inlineStr">
         <is>
           <t>37757</t>
         </is>
@@ -14565,7 +14595,7 @@
           <t>LYU Minzhen</t>
         </is>
       </c>
-      <c r="U247" t="inlineStr">
+      <c r="X247" t="inlineStr">
         <is>
           <t>75379</t>
         </is>
@@ -14623,7 +14653,7 @@
           <t>PELLICER CHICA Laura</t>
         </is>
       </c>
-      <c r="U248" t="inlineStr">
+      <c r="X248" t="inlineStr">
         <is>
           <t>43129</t>
         </is>
@@ -14681,7 +14711,7 @@
           <t>TEUNISSEN Lena</t>
         </is>
       </c>
-      <c r="U249" t="inlineStr">
+      <c r="X249" t="inlineStr">
         <is>
           <t>35344</t>
         </is>
@@ -14739,7 +14769,7 @@
           <t>MILLER Ellis</t>
         </is>
       </c>
-      <c r="U250" t="inlineStr">
+      <c r="X250" t="inlineStr">
         <is>
           <t>75828</t>
         </is>
@@ -14797,7 +14827,7 @@
           <t>BETTERIDGE Lois</t>
         </is>
       </c>
-      <c r="U251" t="inlineStr">
+      <c r="X251" t="inlineStr">
         <is>
           <t>60078</t>
         </is>
@@ -14855,7 +14885,7 @@
           <t>ROISIN Laurene</t>
         </is>
       </c>
-      <c r="U252" t="inlineStr">
+      <c r="X252" t="inlineStr">
         <is>
           <t>76198</t>
         </is>
@@ -14913,7 +14943,7 @@
           <t>MARX Alena</t>
         </is>
       </c>
-      <c r="U253" t="inlineStr">
+      <c r="X253" t="inlineStr">
         <is>
           <t>68844</t>
         </is>
@@ -14971,7 +15001,7 @@
           <t>THOMAS Hannah</t>
         </is>
       </c>
-      <c r="U254" t="inlineStr">
+      <c r="X254" t="inlineStr">
         <is>
           <t>85758</t>
         </is>
@@ -15029,7 +15059,7 @@
           <t>NOVAK Lea</t>
         </is>
       </c>
-      <c r="U255" t="inlineStr">
+      <c r="X255" t="inlineStr">
         <is>
           <t>60323</t>
         </is>
@@ -15087,7 +15117,7 @@
           <t>BAYN Nele</t>
         </is>
       </c>
-      <c r="U256" t="inlineStr">
+      <c r="X256" t="inlineStr">
         <is>
           <t>75442</t>
         </is>
@@ -15145,7 +15175,7 @@
           <t>DOBROTVORSKA Viktoriia</t>
         </is>
       </c>
-      <c r="U257" t="inlineStr">
+      <c r="X257" t="inlineStr">
         <is>
           <t>35526</t>
         </is>
@@ -15203,7 +15233,7 @@
           <t>STANOVSKA Sona</t>
         </is>
       </c>
-      <c r="U258" t="inlineStr">
+      <c r="X258" t="inlineStr">
         <is>
           <t>51647</t>
         </is>
@@ -15261,7 +15291,7 @@
           <t>ZWOLINSKA Klaudia</t>
         </is>
       </c>
-      <c r="U259" t="inlineStr">
+      <c r="X259" t="inlineStr">
         <is>
           <t>42027</t>
         </is>
@@ -15319,7 +15349,7 @@
           <t>LUKNAROVA Emanuela</t>
         </is>
       </c>
-      <c r="U260" t="inlineStr">
+      <c r="X260" t="inlineStr">
         <is>
           <t>76973</t>
         </is>
@@ -15377,7 +15407,7 @@
           <t>LAMEIRO Ainhoa</t>
         </is>
       </c>
-      <c r="U261" t="inlineStr">
+      <c r="X261" t="inlineStr">
         <is>
           <t>69042</t>
         </is>
@@ -15435,7 +15465,7 @@
           <t>LAZKANO Miren</t>
         </is>
       </c>
-      <c r="U262" t="inlineStr">
+      <c r="X262" t="inlineStr">
         <is>
           <t>35748</t>
         </is>
@@ -15493,7 +15523,7 @@
           <t>BORGHI Elena</t>
         </is>
       </c>
-      <c r="U263" t="inlineStr">
+      <c r="X263" t="inlineStr">
         <is>
           <t>75493</t>
         </is>
@@ -15551,7 +15581,7 @@
           <t>BERTONCELLI Marta</t>
         </is>
       </c>
-      <c r="U264" t="inlineStr">
+      <c r="X264" t="inlineStr">
         <is>
           <t>71982</t>
         </is>
@@ -15609,7 +15639,7 @@
           <t>PANKOVA Zuzana</t>
         </is>
       </c>
-      <c r="U265" t="inlineStr">
+      <c r="X265" t="inlineStr">
         <is>
           <t>93906</t>
         </is>
@@ -15667,7 +15697,7 @@
           <t>HOCEVAR Eva Alina</t>
         </is>
       </c>
-      <c r="U266" t="inlineStr">
+      <c r="X266" t="inlineStr">
         <is>
           <t>75533</t>
         </is>
@@ -15725,7 +15755,7 @@
           <t>KOZOROG Alja</t>
         </is>
       </c>
-      <c r="U267" t="inlineStr">
+      <c r="X267" t="inlineStr">
         <is>
           <t>39986</t>
         </is>
@@ -15783,7 +15813,7 @@
           <t>BAUDU Lucie</t>
         </is>
       </c>
-      <c r="U268" t="inlineStr">
+      <c r="X268" t="inlineStr">
         <is>
           <t>35669</t>
         </is>
@@ -15841,7 +15871,7 @@
           <t>OLAZABAL Klara</t>
         </is>
       </c>
-      <c r="U269" t="inlineStr">
+      <c r="X269" t="inlineStr">
         <is>
           <t>43985</t>
         </is>
@@ -15899,7 +15929,7 @@
           <t>US Viktoriia</t>
         </is>
       </c>
-      <c r="U270" t="inlineStr">
+      <c r="X270" t="inlineStr">
         <is>
           <t>35528</t>
         </is>
@@ -15957,7 +15987,7 @@
           <t>SATKOVA Gabriela</t>
         </is>
       </c>
-      <c r="U271" t="inlineStr">
+      <c r="X271" t="inlineStr">
         <is>
           <t>68786</t>
         </is>
@@ -16015,7 +16045,7 @@
           <t>SATKOVA Martina</t>
         </is>
       </c>
-      <c r="U272" t="inlineStr">
+      <c r="X272" t="inlineStr">
         <is>
           <t>42008</t>
         </is>
@@ -16073,7 +16103,7 @@
           <t>FOX Noemie</t>
         </is>
       </c>
-      <c r="U273" t="inlineStr">
+      <c r="X273" t="inlineStr">
         <is>
           <t>44812</t>
         </is>
@@ -16131,7 +16161,7 @@
           <t>DORIA VILARRUBLA Monica</t>
         </is>
       </c>
-      <c r="U274" t="inlineStr">
+      <c r="X274" t="inlineStr">
         <is>
           <t>53051</t>
         </is>
@@ -16189,7 +16219,7 @@
           <t>WOLFFHARDT Viktoria</t>
         </is>
       </c>
-      <c r="U275" t="inlineStr">
+      <c r="X275" t="inlineStr">
         <is>
           <t>35303</t>
         </is>
@@ -16247,7 +16277,7 @@
           <t>DELASSUS Marjorie</t>
         </is>
       </c>
-      <c r="U276" t="inlineStr">
+      <c r="X276" t="inlineStr">
         <is>
           <t>71964</t>
         </is>
@@ -16305,7 +16335,7 @@
           <t>SATILA Ana</t>
         </is>
       </c>
-      <c r="U277" t="inlineStr">
+      <c r="X277" t="inlineStr">
         <is>
           <t>35327</t>
         </is>
@@ -16363,7 +16393,7 @@
           <t>WOODS Kimberley</t>
         </is>
       </c>
-      <c r="U278" t="inlineStr">
+      <c r="X278" t="inlineStr">
         <is>
           <t>35650</t>
         </is>
@@ -16421,7 +16451,7 @@
           <t>LILIK Elena</t>
         </is>
       </c>
-      <c r="U279" t="inlineStr">
+      <c r="X279" t="inlineStr">
         <is>
           <t>51837</t>
         </is>
@@ -16479,7 +16509,7 @@
           <t>HERZOG Andrea</t>
         </is>
       </c>
-      <c r="U280" t="inlineStr">
+      <c r="X280" t="inlineStr">
         <is>
           <t>55099</t>
         </is>
@@ -16537,7 +16567,7 @@
           <t>FISEROVA Tereza</t>
         </is>
       </c>
-      <c r="U281" t="inlineStr">
+      <c r="X281" t="inlineStr">
         <is>
           <t>42016</t>
         </is>
@@ -16595,7 +16625,7 @@
           <t>FRANKLIN Mallory</t>
         </is>
       </c>
-      <c r="U282" t="inlineStr">
+      <c r="X282" t="inlineStr">
         <is>
           <t>35615</t>
         </is>
@@ -16653,7 +16683,7 @@
           <t>FOX Jessica</t>
         </is>
       </c>
-      <c r="U283" t="inlineStr">
+      <c r="X283" t="inlineStr">
         <is>
           <t>36526</t>
         </is>
@@ -16711,7 +16741,7 @@
           <t>LIU Chin-Han</t>
         </is>
       </c>
-      <c r="U284" t="inlineStr">
+      <c r="X284" t="inlineStr">
         <is>
           <t>51894</t>
         </is>
@@ -16769,7 +16799,7 @@
           <t>CHANG Fu-Hua</t>
         </is>
       </c>
-      <c r="U285" t="inlineStr">
+      <c r="X285" t="inlineStr">
         <is>
           <t>122609</t>
         </is>
@@ -16827,7 +16857,7 @@
           <t>FANTINI Tobias</t>
         </is>
       </c>
-      <c r="U286" t="inlineStr">
+      <c r="X286" t="inlineStr">
         <is>
           <t>86982</t>
         </is>
@@ -16885,7 +16915,7 @@
           <t>ZIMMERMAN Isaac</t>
         </is>
       </c>
-      <c r="U287" t="inlineStr">
+      <c r="X287" t="inlineStr">
         <is>
           <t>118723</t>
         </is>
@@ -16943,7 +16973,7 @@
           <t>TRIPANO Nicolas</t>
         </is>
       </c>
-      <c r="U288" t="inlineStr">
+      <c r="X288" t="inlineStr">
         <is>
           <t>83313</t>
         </is>
@@ -17001,7 +17031,7 @@
           <t>ZHANG Zhicheng</t>
         </is>
       </c>
-      <c r="U289" t="inlineStr">
+      <c r="X289" t="inlineStr">
         <is>
           <t>63800</t>
         </is>
@@ -17059,7 +17089,7 @@
           <t>TRIPANO Manuel</t>
         </is>
       </c>
-      <c r="U290" t="inlineStr">
+      <c r="X290" t="inlineStr">
         <is>
           <t>93235</t>
         </is>
@@ -17117,7 +17147,7 @@
           <t>XIE Yuancong</t>
         </is>
       </c>
-      <c r="U291" t="inlineStr">
+      <c r="X291" t="inlineStr">
         <is>
           <t>72214</t>
         </is>
@@ -17175,7 +17205,7 @@
           <t>MCEWAN Devin</t>
         </is>
       </c>
-      <c r="U292" t="inlineStr">
+      <c r="X292" t="inlineStr">
         <is>
           <t>35068</t>
         </is>
@@ -17233,7 +17263,7 @@
           <t>PARRY Daniel</t>
         </is>
       </c>
-      <c r="U293" t="inlineStr">
+      <c r="X293" t="inlineStr">
         <is>
           <t>118725</t>
         </is>
@@ -17291,7 +17321,7 @@
           <t>PUCHNER Oliver</t>
         </is>
       </c>
-      <c r="U294" t="inlineStr">
+      <c r="X294" t="inlineStr">
         <is>
           <t>83529</t>
         </is>
@@ -17349,7 +17379,7 @@
           <t>SAITO Shota</t>
         </is>
       </c>
-      <c r="U295" t="inlineStr">
+      <c r="X295" t="inlineStr">
         <is>
           <t>96090</t>
         </is>
@@ -17407,7 +17437,7 @@
           <t>FRANCIS Nathaniel</t>
         </is>
       </c>
-      <c r="U296" t="inlineStr">
+      <c r="X296" t="inlineStr">
         <is>
           <t>87396</t>
         </is>
@@ -17465,7 +17495,7 @@
           <t>SARAMANDIF Terence</t>
         </is>
       </c>
-      <c r="U297" t="inlineStr">
+      <c r="X297" t="inlineStr">
         <is>
           <t>79340</t>
         </is>
@@ -17523,7 +17553,7 @@
           <t>BURGOS David</t>
         </is>
       </c>
-      <c r="U298" t="inlineStr">
+      <c r="X298" t="inlineStr">
         <is>
           <t>69084</t>
         </is>
@@ -17581,7 +17611,7 @@
           <t>BALDONI Alex</t>
         </is>
       </c>
-      <c r="U299" t="inlineStr">
+      <c r="X299" t="inlineStr">
         <is>
           <t>94528</t>
         </is>
@@ -17639,7 +17669,7 @@
           <t>SASAKI Shota</t>
         </is>
       </c>
-      <c r="U300" t="inlineStr">
+      <c r="X300" t="inlineStr">
         <is>
           <t>41610</t>
         </is>
@@ -17697,7 +17727,7 @@
           <t>KETTLE James</t>
         </is>
       </c>
-      <c r="U301" t="inlineStr">
+      <c r="X301" t="inlineStr">
         <is>
           <t>96006</t>
         </is>
@@ -17755,7 +17785,7 @@
           <t>OTTEN Joris</t>
         </is>
       </c>
-      <c r="U302" t="inlineStr">
+      <c r="X302" t="inlineStr">
         <is>
           <t>41698</t>
         </is>
@@ -17813,7 +17843,7 @@
           <t>KIES Benjamin</t>
         </is>
       </c>
-      <c r="U303" t="inlineStr">
+      <c r="X303" t="inlineStr">
         <is>
           <t>83794</t>
         </is>
@@ -17871,7 +17901,7 @@
           <t>BASSETT Kaylen</t>
         </is>
       </c>
-      <c r="U304" t="inlineStr">
+      <c r="X304" t="inlineStr">
         <is>
           <t>75376</t>
         </is>
@@ -17929,7 +17959,7 @@
           <t>KULIKOV Alexandr</t>
         </is>
       </c>
-      <c r="U305" t="inlineStr">
+      <c r="X305" t="inlineStr">
         <is>
           <t>39679</t>
         </is>
@@ -17987,7 +18017,7 @@
           <t>CRAWFORD Brodie</t>
         </is>
       </c>
-      <c r="U306" t="inlineStr">
+      <c r="X306" t="inlineStr">
         <is>
           <t>38436</t>
         </is>
@@ -18045,7 +18075,7 @@
           <t>CARTER Tristan</t>
         </is>
       </c>
-      <c r="U307" t="inlineStr">
+      <c r="X307" t="inlineStr">
         <is>
           <t>51890</t>
         </is>
@@ -18103,7 +18133,7 @@
           <t>HENDRICK Robert</t>
         </is>
       </c>
-      <c r="U308" t="inlineStr">
+      <c r="X308" t="inlineStr">
         <is>
           <t>43002</t>
         </is>
@@ -18161,7 +18191,7 @@
           <t>BOURHIS Jean Pierre</t>
         </is>
       </c>
-      <c r="U309" t="inlineStr">
+      <c r="X309" t="inlineStr">
         <is>
           <t>36968</t>
         </is>
@@ -18219,7 +18249,7 @@
           <t>TRUMMER Timo</t>
         </is>
       </c>
-      <c r="U310" t="inlineStr">
+      <c r="X310" t="inlineStr">
         <is>
           <t>41599</t>
         </is>
@@ -18277,7 +18307,7 @@
           <t>COCHRANE Jake</t>
         </is>
       </c>
-      <c r="U311" t="inlineStr">
+      <c r="X311" t="inlineStr">
         <is>
           <t>60124</t>
         </is>
@@ -18335,7 +18365,7 @@
           <t>LOKKEN Zachary</t>
         </is>
       </c>
-      <c r="U312" t="inlineStr">
+      <c r="X312" t="inlineStr">
         <is>
           <t>35069</t>
         </is>
@@ -18393,7 +18423,7 @@
           <t>FERNANDEZ Luis</t>
         </is>
       </c>
-      <c r="U313" t="inlineStr">
+      <c r="X313" t="inlineStr">
         <is>
           <t>51851</t>
         </is>
@@ -18451,7 +18481,7 @@
           <t>JEGOU Liam</t>
         </is>
       </c>
-      <c r="U314" t="inlineStr">
+      <c r="X314" t="inlineStr">
         <is>
           <t>35820</t>
         </is>
@@ -18509,7 +18539,7 @@
           <t>DEBLIQUY Mewen</t>
         </is>
       </c>
-      <c r="U315" t="inlineStr">
+      <c r="X315" t="inlineStr">
         <is>
           <t>88656</t>
         </is>
@@ -18567,7 +18597,7 @@
           <t>CECCON Paolo</t>
         </is>
       </c>
-      <c r="U316" t="inlineStr">
+      <c r="X316" t="inlineStr">
         <is>
           <t>39903</t>
         </is>
@@ -18625,7 +18655,7 @@
           <t>TUCHSCHERER Lennard</t>
         </is>
       </c>
-      <c r="U317" t="inlineStr">
+      <c r="X317" t="inlineStr">
         <is>
           <t>60090</t>
         </is>
@@ -18683,7 +18713,7 @@
           <t>KOECHLIN Thomas</t>
         </is>
       </c>
-      <c r="U318" t="inlineStr">
+      <c r="X318" t="inlineStr">
         <is>
           <t>35419</t>
         </is>
@@ -18741,7 +18771,7 @@
           <t>HEGER Vojtech</t>
         </is>
       </c>
-      <c r="U319" t="inlineStr">
+      <c r="X319" t="inlineStr">
         <is>
           <t>68872</t>
         </is>
@@ -18799,7 +18829,7 @@
           <t>HEDWIG Grzegorz</t>
         </is>
       </c>
-      <c r="U320" t="inlineStr">
+      <c r="X320" t="inlineStr">
         <is>
           <t>35465</t>
         </is>
@@ -18857,7 +18887,7 @@
           <t>BERCIC Anze</t>
         </is>
       </c>
-      <c r="U321" t="inlineStr">
+      <c r="X321" t="inlineStr">
         <is>
           <t>36253</t>
         </is>
@@ -18915,7 +18945,7 @@
           <t>COLAZINGARI Roberto</t>
         </is>
       </c>
-      <c r="U322" t="inlineStr">
+      <c r="X322" t="inlineStr">
         <is>
           <t>35223</t>
         </is>
@@ -18973,7 +19003,7 @@
           <t>ROHAN Lukas</t>
         </is>
       </c>
-      <c r="U323" t="inlineStr">
+      <c r="X323" t="inlineStr">
         <is>
           <t>36114</t>
         </is>
@@ -19031,7 +19061,7 @@
           <t>IVALDI Raffaello</t>
         </is>
       </c>
-      <c r="U324" t="inlineStr">
+      <c r="X324" t="inlineStr">
         <is>
           <t>35227</t>
         </is>
@@ -19089,7 +19119,7 @@
           <t>MIRGORODSKY Marko</t>
         </is>
       </c>
-      <c r="U325" t="inlineStr">
+      <c r="X325" t="inlineStr">
         <is>
           <t>42019</t>
         </is>
@@ -19147,7 +19177,7 @@
           <t>MARTIKAN Michal</t>
         </is>
       </c>
-      <c r="U326" t="inlineStr">
+      <c r="X326" t="inlineStr">
         <is>
           <t>35365</t>
         </is>
@@ -19205,7 +19235,7 @@
           <t>TRAVE Miquel</t>
         </is>
       </c>
-      <c r="U327" t="inlineStr">
+      <c r="X327" t="inlineStr">
         <is>
           <t>68998</t>
         </is>
@@ -19263,7 +19293,7 @@
           <t>WESTLEY Ryan</t>
         </is>
       </c>
-      <c r="U328" t="inlineStr">
+      <c r="X328" t="inlineStr">
         <is>
           <t>35651</t>
         </is>
@@ -19321,7 +19351,7 @@
           <t>BURGESS Adam</t>
         </is>
       </c>
-      <c r="U329" t="inlineStr">
+      <c r="X329" t="inlineStr">
         <is>
           <t>35647</t>
         </is>
@@ -19379,7 +19409,7 @@
           <t>GESTIN Nicolas</t>
         </is>
       </c>
-      <c r="U330" t="inlineStr">
+      <c r="X330" t="inlineStr">
         <is>
           <t>71961</t>
         </is>
@@ -19437,7 +19467,7 @@
           <t>CHALOUPKA Vaclav</t>
         </is>
       </c>
-      <c r="U331" t="inlineStr">
+      <c r="X331" t="inlineStr">
         <is>
           <t>51648</t>
         </is>
@@ -19495,7 +19525,7 @@
           <t>GARGAUD CHANUT Denis</t>
         </is>
       </c>
-      <c r="U332" t="inlineStr">
+      <c r="X332" t="inlineStr">
         <is>
           <t>35177</t>
         </is>
@@ -19553,7 +19583,7 @@
           <t>BENUS Matej</t>
         </is>
       </c>
-      <c r="U333" t="inlineStr">
+      <c r="X333" t="inlineStr">
         <is>
           <t>35353</t>
         </is>
@@ -19611,7 +19641,7 @@
           <t>BOZIC Luka</t>
         </is>
       </c>
-      <c r="U334" t="inlineStr">
+      <c r="X334" t="inlineStr">
         <is>
           <t>36269</t>
         </is>
@@ -19669,7 +19699,7 @@
           <t>SAVSEK Benjamin</t>
         </is>
       </c>
-      <c r="U335" t="inlineStr">
+      <c r="X335" t="inlineStr">
         <is>
           <t>36218</t>
         </is>
@@ -19727,7 +19757,7 @@
           <t>CEJAS Macarena</t>
         </is>
       </c>
-      <c r="U336" t="inlineStr">
+      <c r="X336" t="inlineStr">
         <is>
           <t>93234</t>
         </is>
@@ -19785,7 +19815,7 @@
           <t>CHOU Chih-Chin</t>
         </is>
       </c>
-      <c r="U337" t="inlineStr">
+      <c r="X337" t="inlineStr">
         <is>
           <t>68975</t>
         </is>
@@ -19843,7 +19873,7 @@
           <t>OKAZAKI Haruka</t>
         </is>
       </c>
-      <c r="U338" t="inlineStr">
+      <c r="X338" t="inlineStr">
         <is>
           <t>42265</t>
         </is>
@@ -19901,7 +19931,7 @@
           <t>CHEN Wei-Han</t>
         </is>
       </c>
-      <c r="U339" t="inlineStr">
+      <c r="X339" t="inlineStr">
         <is>
           <t>61630</t>
         </is>
@@ -19959,7 +19989,7 @@
           <t>HUANG Yanzhi</t>
         </is>
       </c>
-      <c r="U340" t="inlineStr">
+      <c r="X340" t="inlineStr">
         <is>
           <t>106165</t>
         </is>
@@ -20017,7 +20047,7 @@
           <t>YANG Liu</t>
         </is>
       </c>
-      <c r="U341" t="inlineStr">
+      <c r="X341" t="inlineStr">
         <is>
           <t>87649</t>
         </is>
@@ -20075,7 +20105,7 @@
           <t>MISHIMA Ren</t>
         </is>
       </c>
-      <c r="U342" t="inlineStr">
+      <c r="X342" t="inlineStr">
         <is>
           <t>37757</t>
         </is>
@@ -20133,7 +20163,7 @@
           <t>LYU Minzhen</t>
         </is>
       </c>
-      <c r="U343" t="inlineStr">
+      <c r="X343" t="inlineStr">
         <is>
           <t>75379</t>
         </is>
@@ -20191,7 +20221,7 @@
           <t>PELLICER CHICA Laura</t>
         </is>
       </c>
-      <c r="U344" t="inlineStr">
+      <c r="X344" t="inlineStr">
         <is>
           <t>43129</t>
         </is>
@@ -20249,7 +20279,7 @@
           <t>TEUNISSEN Lena</t>
         </is>
       </c>
-      <c r="U345" t="inlineStr">
+      <c r="X345" t="inlineStr">
         <is>
           <t>35344</t>
         </is>
@@ -20307,7 +20337,7 @@
           <t>MILLER Ellis</t>
         </is>
       </c>
-      <c r="U346" t="inlineStr">
+      <c r="X346" t="inlineStr">
         <is>
           <t>75828</t>
         </is>
@@ -20365,7 +20395,7 @@
           <t>BETTERIDGE Lois</t>
         </is>
       </c>
-      <c r="U347" t="inlineStr">
+      <c r="X347" t="inlineStr">
         <is>
           <t>60078</t>
         </is>
@@ -20423,7 +20453,7 @@
           <t>THOMAS Hannah</t>
         </is>
       </c>
-      <c r="U348" t="inlineStr">
+      <c r="X348" t="inlineStr">
         <is>
           <t>85758</t>
         </is>
@@ -20481,7 +20511,7 @@
           <t>BAYN Nele</t>
         </is>
       </c>
-      <c r="U349" t="inlineStr">
+      <c r="X349" t="inlineStr">
         <is>
           <t>75442</t>
         </is>
@@ -20539,7 +20569,7 @@
           <t>DOBROTVORSKA Viktoriia</t>
         </is>
       </c>
-      <c r="U350" t="inlineStr">
+      <c r="X350" t="inlineStr">
         <is>
           <t>35526</t>
         </is>
@@ -20597,7 +20627,7 @@
           <t>STANOVSKA Sona</t>
         </is>
       </c>
-      <c r="U351" t="inlineStr">
+      <c r="X351" t="inlineStr">
         <is>
           <t>51647</t>
         </is>
@@ -20655,7 +20685,7 @@
           <t>ZWOLINSKA Klaudia</t>
         </is>
       </c>
-      <c r="U352" t="inlineStr">
+      <c r="X352" t="inlineStr">
         <is>
           <t>42027</t>
         </is>
@@ -20713,7 +20743,7 @@
           <t>LUKNAROVA Emanuela</t>
         </is>
       </c>
-      <c r="U353" t="inlineStr">
+      <c r="X353" t="inlineStr">
         <is>
           <t>76973</t>
         </is>
@@ -20771,7 +20801,7 @@
           <t>PANKOVA Zuzana</t>
         </is>
       </c>
-      <c r="U354" t="inlineStr">
+      <c r="X354" t="inlineStr">
         <is>
           <t>93906</t>
         </is>
@@ -20829,7 +20859,7 @@
           <t>HOCEVAR Eva Alina</t>
         </is>
       </c>
-      <c r="U355" t="inlineStr">
+      <c r="X355" t="inlineStr">
         <is>
           <t>75533</t>
         </is>
@@ -20887,7 +20917,7 @@
           <t>KOZOROG Alja</t>
         </is>
       </c>
-      <c r="U356" t="inlineStr">
+      <c r="X356" t="inlineStr">
         <is>
           <t>39986</t>
         </is>
@@ -20945,7 +20975,7 @@
           <t>BAUDU Lucie</t>
         </is>
       </c>
-      <c r="U357" t="inlineStr">
+      <c r="X357" t="inlineStr">
         <is>
           <t>35669</t>
         </is>
@@ -21003,7 +21033,7 @@
           <t>FOX Noemie</t>
         </is>
       </c>
-      <c r="U358" t="inlineStr">
+      <c r="X358" t="inlineStr">
         <is>
           <t>44812</t>
         </is>
@@ -21061,7 +21091,7 @@
           <t>WOLFFHARDT Viktoria</t>
         </is>
       </c>
-      <c r="U359" t="inlineStr">
+      <c r="X359" t="inlineStr">
         <is>
           <t>35303</t>
         </is>
@@ -21119,7 +21149,7 @@
           <t>LIU Chin-Han</t>
         </is>
       </c>
-      <c r="U360" t="inlineStr">
+      <c r="X360" t="inlineStr">
         <is>
           <t>51894</t>
         </is>
@@ -21177,7 +21207,7 @@
           <t>CHANG Fu-Hua</t>
         </is>
       </c>
-      <c r="U361" t="inlineStr">
+      <c r="X361" t="inlineStr">
         <is>
           <t>122609</t>
         </is>
@@ -21235,7 +21265,7 @@
           <t>FANTINI Tobias</t>
         </is>
       </c>
-      <c r="U362" t="inlineStr">
+      <c r="X362" t="inlineStr">
         <is>
           <t>86982</t>
         </is>
@@ -21293,7 +21323,7 @@
           <t>ZIMMERMAN Isaac</t>
         </is>
       </c>
-      <c r="U363" t="inlineStr">
+      <c r="X363" t="inlineStr">
         <is>
           <t>118723</t>
         </is>
@@ -21351,7 +21381,7 @@
           <t>TRIPANO Nicolas</t>
         </is>
       </c>
-      <c r="U364" t="inlineStr">
+      <c r="X364" t="inlineStr">
         <is>
           <t>83313</t>
         </is>
@@ -21409,7 +21439,7 @@
           <t>ZHANG Zhicheng</t>
         </is>
       </c>
-      <c r="U365" t="inlineStr">
+      <c r="X365" t="inlineStr">
         <is>
           <t>63800</t>
         </is>
@@ -21467,7 +21497,7 @@
           <t>TRIPANO Manuel</t>
         </is>
       </c>
-      <c r="U366" t="inlineStr">
+      <c r="X366" t="inlineStr">
         <is>
           <t>93235</t>
         </is>
@@ -21525,7 +21555,7 @@
           <t>XIE Yuancong</t>
         </is>
       </c>
-      <c r="U367" t="inlineStr">
+      <c r="X367" t="inlineStr">
         <is>
           <t>72214</t>
         </is>
@@ -21583,7 +21613,7 @@
           <t>MCEWAN Devin</t>
         </is>
       </c>
-      <c r="U368" t="inlineStr">
+      <c r="X368" t="inlineStr">
         <is>
           <t>35068</t>
         </is>
@@ -21641,7 +21671,7 @@
           <t>PARRY Daniel</t>
         </is>
       </c>
-      <c r="U369" t="inlineStr">
+      <c r="X369" t="inlineStr">
         <is>
           <t>118725</t>
         </is>
@@ -21699,7 +21729,7 @@
           <t>PUCHNER Oliver</t>
         </is>
       </c>
-      <c r="U370" t="inlineStr">
+      <c r="X370" t="inlineStr">
         <is>
           <t>83529</t>
         </is>
@@ -21757,7 +21787,7 @@
           <t>SAITO Shota</t>
         </is>
       </c>
-      <c r="U371" t="inlineStr">
+      <c r="X371" t="inlineStr">
         <is>
           <t>96090</t>
         </is>
@@ -21815,7 +21845,7 @@
           <t>FRANCIS Nathaniel</t>
         </is>
       </c>
-      <c r="U372" t="inlineStr">
+      <c r="X372" t="inlineStr">
         <is>
           <t>87396</t>
         </is>
@@ -21873,7 +21903,7 @@
           <t>SARAMANDIF Terence</t>
         </is>
       </c>
-      <c r="U373" t="inlineStr">
+      <c r="X373" t="inlineStr">
         <is>
           <t>79340</t>
         </is>
@@ -21931,7 +21961,7 @@
           <t>BURGOS David</t>
         </is>
       </c>
-      <c r="U374" t="inlineStr">
+      <c r="X374" t="inlineStr">
         <is>
           <t>69084</t>
         </is>
@@ -21989,7 +22019,7 @@
           <t>BALDONI Alex</t>
         </is>
       </c>
-      <c r="U375" t="inlineStr">
+      <c r="X375" t="inlineStr">
         <is>
           <t>94528</t>
         </is>
@@ -22047,7 +22077,7 @@
           <t>SASAKI Shota</t>
         </is>
       </c>
-      <c r="U376" t="inlineStr">
+      <c r="X376" t="inlineStr">
         <is>
           <t>41610</t>
         </is>
@@ -22105,7 +22135,7 @@
           <t>KETTLE James</t>
         </is>
       </c>
-      <c r="U377" t="inlineStr">
+      <c r="X377" t="inlineStr">
         <is>
           <t>96006</t>
         </is>
@@ -22163,7 +22193,7 @@
           <t>OTTEN Joris</t>
         </is>
       </c>
-      <c r="U378" t="inlineStr">
+      <c r="X378" t="inlineStr">
         <is>
           <t>41698</t>
         </is>
@@ -22221,7 +22251,7 @@
           <t>KIES Benjamin</t>
         </is>
       </c>
-      <c r="U379" t="inlineStr">
+      <c r="X379" t="inlineStr">
         <is>
           <t>83794</t>
         </is>
@@ -22279,7 +22309,7 @@
           <t>BASSETT Kaylen</t>
         </is>
       </c>
-      <c r="U380" t="inlineStr">
+      <c r="X380" t="inlineStr">
         <is>
           <t>75376</t>
         </is>
@@ -22337,7 +22367,7 @@
           <t>KULIKOV Alexandr</t>
         </is>
       </c>
-      <c r="U381" t="inlineStr">
+      <c r="X381" t="inlineStr">
         <is>
           <t>39679</t>
         </is>
@@ -22395,7 +22425,7 @@
           <t>CRAWFORD Brodie</t>
         </is>
       </c>
-      <c r="U382" t="inlineStr">
+      <c r="X382" t="inlineStr">
         <is>
           <t>38436</t>
         </is>
@@ -22453,7 +22483,7 @@
           <t>HENDRICK Robert</t>
         </is>
       </c>
-      <c r="U383" t="inlineStr">
+      <c r="X383" t="inlineStr">
         <is>
           <t>43002</t>
         </is>
@@ -22511,7 +22541,7 @@
           <t>BOURHIS Jean Pierre</t>
         </is>
       </c>
-      <c r="U384" t="inlineStr">
+      <c r="X384" t="inlineStr">
         <is>
           <t>36968</t>
         </is>
@@ -22569,7 +22599,7 @@
           <t>TRUMMER Timo</t>
         </is>
       </c>
-      <c r="U385" t="inlineStr">
+      <c r="X385" t="inlineStr">
         <is>
           <t>41599</t>
         </is>
@@ -22627,7 +22657,7 @@
           <t>COCHRANE Jake</t>
         </is>
       </c>
-      <c r="U386" t="inlineStr">
+      <c r="X386" t="inlineStr">
         <is>
           <t>60124</t>
         </is>
@@ -22685,7 +22715,7 @@
           <t>KOECHLIN Thomas</t>
         </is>
       </c>
-      <c r="U387" t="inlineStr">
+      <c r="X387" t="inlineStr">
         <is>
           <t>35419</t>
         </is>
@@ -22743,7 +22773,7 @@
           <t>HEGER Vojtech</t>
         </is>
       </c>
-      <c r="U388" t="inlineStr">
+      <c r="X388" t="inlineStr">
         <is>
           <t>68872</t>
         </is>
@@ -22801,7 +22831,7 @@
           <t>BERCIC Anze</t>
         </is>
       </c>
-      <c r="U389" t="inlineStr">
+      <c r="X389" t="inlineStr">
         <is>
           <t>36253</t>
         </is>
@@ -22859,7 +22889,7 @@
           <t>MARTIKAN Michal</t>
         </is>
       </c>
-      <c r="U390" t="inlineStr">
+      <c r="X390" t="inlineStr">
         <is>
           <t>35365</t>
         </is>
@@ -22917,7 +22947,7 @@
           <t>BURGESS Adam</t>
         </is>
       </c>
-      <c r="U391" t="inlineStr">
+      <c r="X391" t="inlineStr">
         <is>
           <t>35647</t>
         </is>
@@ -23945,7 +23975,7 @@
           <t>VALIKOVA Barbora</t>
         </is>
       </c>
-      <c r="U412" t="inlineStr">
+      <c r="X412" t="inlineStr">
         <is>
           <t>37267</t>
         </is>
@@ -24003,7 +24033,7 @@
           <t>NOVAK Ajda</t>
         </is>
       </c>
-      <c r="U413" t="inlineStr">
+      <c r="X413" t="inlineStr">
         <is>
           <t>39079</t>
         </is>
@@ -24061,7 +24091,7 @@
           <t>FOX Noemie</t>
         </is>
       </c>
-      <c r="U414" t="inlineStr">
+      <c r="X414" t="inlineStr">
         <is>
           <t>44812</t>
         </is>
@@ -24119,7 +24149,7 @@
           <t>WEGMAN Martina</t>
         </is>
       </c>
-      <c r="U415" t="inlineStr">
+      <c r="X415" t="inlineStr">
         <is>
           <t>35345</t>
         </is>
@@ -24177,7 +24207,7 @@
           <t>YAN Jiahua</t>
         </is>
       </c>
-      <c r="U416" t="inlineStr">
+      <c r="X416" t="inlineStr">
         <is>
           <t>43545</t>
         </is>
@@ -24235,7 +24265,7 @@
           <t>HOCEVAR Eva Alina</t>
         </is>
       </c>
-      <c r="U417" t="inlineStr">
+      <c r="X417" t="inlineStr">
         <is>
           <t>75533</t>
         </is>
@@ -24293,7 +24323,7 @@
           <t>APEL Emily</t>
         </is>
       </c>
-      <c r="U418" t="inlineStr">
+      <c r="X418" t="inlineStr">
         <is>
           <t>83788</t>
         </is>
@@ -24351,7 +24381,7 @@
           <t>PACIERPNIK Natalia</t>
         </is>
       </c>
-      <c r="U419" t="inlineStr">
+      <c r="X419" t="inlineStr">
         <is>
           <t>35077</t>
         </is>
@@ -24409,7 +24439,7 @@
           <t>FISEROVA Tereza</t>
         </is>
       </c>
-      <c r="U420" t="inlineStr">
+      <c r="X420" t="inlineStr">
         <is>
           <t>42016</t>
         </is>
@@ -24467,7 +24497,7 @@
           <t>LILIK Elena</t>
         </is>
       </c>
-      <c r="U421" t="inlineStr">
+      <c r="X421" t="inlineStr">
         <is>
           <t>51837</t>
         </is>
@@ -24525,7 +24555,7 @@
           <t>GALUSKOVA Antonie</t>
         </is>
       </c>
-      <c r="U422" t="inlineStr">
+      <c r="X422" t="inlineStr">
         <is>
           <t>68754</t>
         </is>
@@ -24583,7 +24613,7 @@
           <t>PANKOVA Zuzana</t>
         </is>
       </c>
-      <c r="U423" t="inlineStr">
+      <c r="X423" t="inlineStr">
         <is>
           <t>93906</t>
         </is>
@@ -24641,7 +24671,7 @@
           <t>DORIA VILARRUBLA Monica</t>
         </is>
       </c>
-      <c r="U424" t="inlineStr">
+      <c r="X424" t="inlineStr">
         <is>
           <t>53051</t>
         </is>
@@ -24699,7 +24729,7 @@
           <t>WOODS Kimberley</t>
         </is>
       </c>
-      <c r="U425" t="inlineStr">
+      <c r="X425" t="inlineStr">
         <is>
           <t>35650</t>
         </is>
@@ -24757,7 +24787,7 @@
           <t>KUHNLE Corinna</t>
         </is>
       </c>
-      <c r="U426" t="inlineStr">
+      <c r="X426" t="inlineStr">
         <is>
           <t>35282</t>
         </is>
@@ -24815,7 +24845,7 @@
           <t>SORRIBES Laia</t>
         </is>
       </c>
-      <c r="U427" t="inlineStr">
+      <c r="X427" t="inlineStr">
         <is>
           <t>68822</t>
         </is>
@@ -24873,7 +24903,7 @@
           <t>BOUZIDI Carole</t>
         </is>
       </c>
-      <c r="U428" t="inlineStr">
+      <c r="X428" t="inlineStr">
         <is>
           <t>118428</t>
         </is>
@@ -24931,7 +24961,7 @@
           <t>WOLFFHARDT Viktoria</t>
         </is>
       </c>
-      <c r="U429" t="inlineStr">
+      <c r="X429" t="inlineStr">
         <is>
           <t>35303</t>
         </is>
@@ -24989,7 +25019,7 @@
           <t>TERCELJ Eva</t>
         </is>
       </c>
-      <c r="U430" t="inlineStr">
+      <c r="X430" t="inlineStr">
         <is>
           <t>36263</t>
         </is>
@@ -25047,7 +25077,7 @@
           <t>PRIGENT Camille</t>
         </is>
       </c>
-      <c r="U431" t="inlineStr">
+      <c r="X431" t="inlineStr">
         <is>
           <t>41566</t>
         </is>
@@ -25105,7 +25135,7 @@
           <t>TEUNISSEN Lena</t>
         </is>
       </c>
-      <c r="U432" t="inlineStr">
+      <c r="X432" t="inlineStr">
         <is>
           <t>35344</t>
         </is>
@@ -25163,7 +25193,7 @@
           <t>VUITTON Emma</t>
         </is>
       </c>
-      <c r="U433" t="inlineStr">
+      <c r="X433" t="inlineStr">
         <is>
           <t>84126</t>
         </is>
@@ -25221,7 +25251,7 @@
           <t>ZWOLINSKA Klaudia</t>
         </is>
       </c>
-      <c r="U434" t="inlineStr">
+      <c r="X434" t="inlineStr">
         <is>
           <t>42027</t>
         </is>
@@ -25279,7 +25309,7 @@
           <t>US Viktoriia</t>
         </is>
       </c>
-      <c r="U435" t="inlineStr">
+      <c r="X435" t="inlineStr">
         <is>
           <t>35528</t>
         </is>
@@ -25337,7 +25367,7 @@
           <t>CHOURRAUT Maialen</t>
         </is>
       </c>
-      <c r="U436" t="inlineStr">
+      <c r="X436" t="inlineStr">
         <is>
           <t>35787</t>
         </is>
@@ -25395,7 +25425,7 @@
           <t>PRIGENT Romane</t>
         </is>
       </c>
-      <c r="U437" t="inlineStr">
+      <c r="X437" t="inlineStr">
         <is>
           <t>71968</t>
         </is>
@@ -25453,7 +25483,7 @@
           <t>HORN Stefanie</t>
         </is>
       </c>
-      <c r="U438" t="inlineStr">
+      <c r="X438" t="inlineStr">
         <is>
           <t>38417</t>
         </is>
@@ -25511,7 +25541,7 @@
           <t>FRANKLIN Mallory</t>
         </is>
       </c>
-      <c r="U439" t="inlineStr">
+      <c r="X439" t="inlineStr">
         <is>
           <t>35615</t>
         </is>
@@ -25569,7 +25599,7 @@
           <t>FUNK Ricarda</t>
         </is>
       </c>
-      <c r="U440" t="inlineStr">
+      <c r="X440" t="inlineStr">
         <is>
           <t>35122</t>
         </is>
@@ -25627,7 +25657,7 @@
           <t>FOX Jessica</t>
         </is>
       </c>
-      <c r="U441" t="inlineStr">
+      <c r="X441" t="inlineStr">
         <is>
           <t>36526</t>
         </is>
@@ -25685,7 +25715,7 @@
           <t>HALCIN Martin</t>
         </is>
       </c>
-      <c r="U442" t="inlineStr">
+      <c r="X442" t="inlineStr">
         <is>
           <t>35355</t>
         </is>
@@ -25743,7 +25773,7 @@
           <t>HUANG Liman</t>
         </is>
       </c>
-      <c r="U443" t="inlineStr">
+      <c r="X443" t="inlineStr">
         <is>
           <t>118848</t>
         </is>
@@ -25801,7 +25831,7 @@
           <t>POPE Benjamin</t>
         </is>
       </c>
-      <c r="U444" t="inlineStr">
+      <c r="X444" t="inlineStr">
         <is>
           <t>51753</t>
         </is>
@@ -25859,7 +25889,7 @@
           <t>DICKSON Jonny</t>
         </is>
       </c>
-      <c r="U445" t="inlineStr">
+      <c r="X445" t="inlineStr">
         <is>
           <t>75973</t>
         </is>
@@ -25917,7 +25947,7 @@
           <t>ROSSI Lucas</t>
         </is>
       </c>
-      <c r="U446" t="inlineStr">
+      <c r="X446" t="inlineStr">
         <is>
           <t>36925</t>
         </is>
@@ -25975,7 +26005,7 @@
           <t>TUNKA Ondrej</t>
         </is>
       </c>
-      <c r="U447" t="inlineStr">
+      <c r="X447" t="inlineStr">
         <is>
           <t>35947</t>
         </is>
@@ -26033,7 +26063,7 @@
           <t>IVALDI Zeno</t>
         </is>
       </c>
-      <c r="U448" t="inlineStr">
+      <c r="X448" t="inlineStr">
         <is>
           <t>35480</t>
         </is>
@@ -26091,7 +26121,7 @@
           <t>POPIELA Dariusz</t>
         </is>
       </c>
-      <c r="U449" t="inlineStr">
+      <c r="X449" t="inlineStr">
         <is>
           <t>35096</t>
         </is>
@@ -26149,7 +26179,7 @@
           <t>BEDA Marcello</t>
         </is>
       </c>
-      <c r="U450" t="inlineStr">
+      <c r="X450" t="inlineStr">
         <is>
           <t>39899</t>
         </is>
@@ -26207,7 +26237,7 @@
           <t>SRABOTNIK Martin</t>
         </is>
       </c>
-      <c r="U451" t="inlineStr">
+      <c r="X451" t="inlineStr">
         <is>
           <t>39080</t>
         </is>
@@ -26265,7 +26295,7 @@
           <t>OHRSTROM Isak</t>
         </is>
       </c>
-      <c r="U452" t="inlineStr">
+      <c r="X452" t="inlineStr">
         <is>
           <t>35101</t>
         </is>
@@ -26323,7 +26353,7 @@
           <t>GONCALVES Pedro</t>
         </is>
       </c>
-      <c r="U453" t="inlineStr">
+      <c r="X453" t="inlineStr">
         <is>
           <t>38017</t>
         </is>
@@ -26381,7 +26411,7 @@
           <t>MUTO Yusuke</t>
         </is>
       </c>
-      <c r="U454" t="inlineStr">
+      <c r="X454" t="inlineStr">
         <is>
           <t>71820</t>
         </is>
@@ -26439,7 +26469,7 @@
           <t>WERRO Lukas</t>
         </is>
       </c>
-      <c r="U455" t="inlineStr">
+      <c r="X455" t="inlineStr">
         <is>
           <t>35347</t>
         </is>
@@ -26497,7 +26527,7 @@
           <t>ANDERSON Timothy</t>
         </is>
       </c>
-      <c r="U456" t="inlineStr">
+      <c r="X456" t="inlineStr">
         <is>
           <t>38432</t>
         </is>
@@ -26555,7 +26585,7 @@
           <t>OSCHMAUTZ Felix</t>
         </is>
       </c>
-      <c r="U457" t="inlineStr">
+      <c r="X457" t="inlineStr">
         <is>
           <t>51856</t>
         </is>
@@ -26613,7 +26643,7 @@
           <t>KAUZER Peter</t>
         </is>
       </c>
-      <c r="U458" t="inlineStr">
+      <c r="X458" t="inlineStr">
         <is>
           <t>35589</t>
         </is>
@@ -26671,7 +26701,7 @@
           <t>ADACHI Kazuya</t>
         </is>
       </c>
-      <c r="U459" t="inlineStr">
+      <c r="X459" t="inlineStr">
         <is>
           <t>36646</t>
         </is>
@@ -26729,7 +26759,7 @@
           <t>CASTRYCK Titouan</t>
         </is>
       </c>
-      <c r="U460" t="inlineStr">
+      <c r="X460" t="inlineStr">
         <is>
           <t>88701</t>
         </is>
@@ -26787,7 +26817,7 @@
           <t>BREMER Tim</t>
         </is>
       </c>
-      <c r="U461" t="inlineStr">
+      <c r="X461" t="inlineStr">
         <is>
           <t>84001</t>
         </is>
@@ -26845,7 +26875,7 @@
           <t>DOUGOUD Martin</t>
         </is>
       </c>
-      <c r="U462" t="inlineStr">
+      <c r="X462" t="inlineStr">
         <is>
           <t>35426</t>
         </is>
@@ -26903,7 +26933,7 @@
           <t>HEGGE Noah</t>
         </is>
       </c>
-      <c r="U463" t="inlineStr">
+      <c r="X463" t="inlineStr">
         <is>
           <t>71837</t>
         </is>
@@ -26961,7 +26991,7 @@
           <t>DELFOUR Lucien</t>
         </is>
       </c>
-      <c r="U464" t="inlineStr">
+      <c r="X464" t="inlineStr">
         <is>
           <t>36537</t>
         </is>
@@ -27019,7 +27049,7 @@
           <t>BRZEZINSKI Jakub</t>
         </is>
       </c>
-      <c r="U465" t="inlineStr">
+      <c r="X465" t="inlineStr">
         <is>
           <t>43977</t>
         </is>
@@ -27077,7 +27107,7 @@
           <t>NEVEU Boris</t>
         </is>
       </c>
-      <c r="U466" t="inlineStr">
+      <c r="X466" t="inlineStr">
         <is>
           <t>35396</t>
         </is>
@@ -27135,7 +27165,7 @@
           <t>DE GENNARO Giovanni</t>
         </is>
       </c>
-      <c r="U467" t="inlineStr">
+      <c r="X467" t="inlineStr">
         <is>
           <t>35244</t>
         </is>
@@ -27193,7 +27223,7 @@
           <t>CHIARELLO Gelindo</t>
         </is>
       </c>
-      <c r="U468" t="inlineStr">
+      <c r="X468" t="inlineStr">
         <is>
           <t>39956</t>
         </is>
@@ -27251,7 +27281,7 @@
           <t>HENDRICK Noel</t>
         </is>
       </c>
-      <c r="U469" t="inlineStr">
+      <c r="X469" t="inlineStr">
         <is>
           <t>43003</t>
         </is>
@@ -27309,7 +27339,7 @@
           <t>QUEMENEUR Malo</t>
         </is>
       </c>
-      <c r="U470" t="inlineStr">
+      <c r="X470" t="inlineStr">
         <is>
           <t>60403</t>
         </is>
@@ -27367,7 +27397,7 @@
           <t>PASIUT Michal</t>
         </is>
       </c>
-      <c r="U471" t="inlineStr">
+      <c r="X471" t="inlineStr">
         <is>
           <t>35095</t>
         </is>
@@ -27425,7 +27455,7 @@
           <t>BUTCHER Finn</t>
         </is>
       </c>
-      <c r="U472" t="inlineStr">
+      <c r="X472" t="inlineStr">
         <is>
           <t>36663</t>
         </is>
@@ -27483,7 +27513,7 @@
           <t>QUAN Xin</t>
         </is>
       </c>
-      <c r="U473" t="inlineStr">
+      <c r="X473" t="inlineStr">
         <is>
           <t>62343</t>
         </is>
@@ -27541,7 +27571,7 @@
           <t>OCHOA Manuel</t>
         </is>
       </c>
-      <c r="U474" t="inlineStr">
+      <c r="X474" t="inlineStr">
         <is>
           <t>69081</t>
         </is>
@@ -27599,7 +27629,7 @@
           <t>CLARKE Joseph</t>
         </is>
       </c>
-      <c r="U475" t="inlineStr">
+      <c r="X475" t="inlineStr">
         <is>
           <t>35654</t>
         </is>
@@ -27657,7 +27687,7 @@
           <t>LEITNER Mario</t>
         </is>
       </c>
-      <c r="U476" t="inlineStr">
+      <c r="X476" t="inlineStr">
         <is>
           <t>35546</t>
         </is>
@@ -27715,7 +27745,7 @@
           <t>HENGST Stefan</t>
         </is>
       </c>
-      <c r="U477" t="inlineStr">
+      <c r="X477" t="inlineStr">
         <is>
           <t>39061</t>
         </is>
@@ -27773,7 +27803,7 @@
           <t>PRINDIS Vit</t>
         </is>
       </c>
-      <c r="U478" t="inlineStr">
+      <c r="X478" t="inlineStr">
         <is>
           <t>35065</t>
         </is>
@@ -27831,7 +27861,7 @@
           <t>TRAVE Miquel</t>
         </is>
       </c>
-      <c r="U479" t="inlineStr">
+      <c r="X479" t="inlineStr">
         <is>
           <t>68998</t>
         </is>
@@ -27889,7 +27919,7 @@
           <t>CRESPO Joan</t>
         </is>
       </c>
-      <c r="U480" t="inlineStr">
+      <c r="X480" t="inlineStr">
         <is>
           <t>35749</t>
         </is>
@@ -27947,7 +27977,7 @@
           <t>PRSKAVEC Jiri</t>
         </is>
       </c>
-      <c r="U481" t="inlineStr">
+      <c r="X481" t="inlineStr">
         <is>
           <t>35033</t>
         </is>
@@ -28015,7 +28045,7 @@
           <t>WEGMAN Martina</t>
         </is>
       </c>
-      <c r="U482" t="inlineStr">
+      <c r="X482" t="inlineStr">
         <is>
           <t>35345</t>
         </is>
@@ -28083,7 +28113,7 @@
           <t>NOVAK Ajda</t>
         </is>
       </c>
-      <c r="U483" t="inlineStr">
+      <c r="X483" t="inlineStr">
         <is>
           <t>39079</t>
         </is>
@@ -28151,7 +28181,7 @@
           <t>TEUNISSEN Lena</t>
         </is>
       </c>
-      <c r="U484" t="inlineStr">
+      <c r="X484" t="inlineStr">
         <is>
           <t>35344</t>
         </is>
@@ -28219,7 +28249,7 @@
           <t>DORIA VILARRUBLA Monica</t>
         </is>
       </c>
-      <c r="U485" t="inlineStr">
+      <c r="X485" t="inlineStr">
         <is>
           <t>53051</t>
         </is>
@@ -28287,7 +28317,7 @@
           <t>WOODS Kimberley</t>
         </is>
       </c>
-      <c r="U486" t="inlineStr">
+      <c r="X486" t="inlineStr">
         <is>
           <t>35650</t>
         </is>
@@ -28355,7 +28385,7 @@
           <t>FRANKLIN Mallory</t>
         </is>
       </c>
-      <c r="U487" t="inlineStr">
+      <c r="X487" t="inlineStr">
         <is>
           <t>35615</t>
         </is>
@@ -28423,7 +28453,7 @@
           <t>PRIGENT Camille</t>
         </is>
       </c>
-      <c r="U488" t="inlineStr">
+      <c r="X488" t="inlineStr">
         <is>
           <t>41566</t>
         </is>
@@ -28491,7 +28521,7 @@
           <t>FUNK Ricarda</t>
         </is>
       </c>
-      <c r="U489" t="inlineStr">
+      <c r="X489" t="inlineStr">
         <is>
           <t>35122</t>
         </is>
@@ -28559,7 +28589,7 @@
           <t>HORN Stefanie</t>
         </is>
       </c>
-      <c r="U490" t="inlineStr">
+      <c r="X490" t="inlineStr">
         <is>
           <t>38417</t>
         </is>
@@ -28627,7 +28657,7 @@
           <t>CHOURRAUT Maialen</t>
         </is>
       </c>
-      <c r="U491" t="inlineStr">
+      <c r="X491" t="inlineStr">
         <is>
           <t>35787</t>
         </is>
@@ -28695,7 +28725,7 @@
           <t>PRINDIS Vit</t>
         </is>
       </c>
-      <c r="U492" t="inlineStr">
+      <c r="X492" t="inlineStr">
         <is>
           <t>35065</t>
         </is>
@@ -28763,7 +28793,7 @@
           <t>SRABOTNIK Martin</t>
         </is>
       </c>
-      <c r="U493" t="inlineStr">
+      <c r="X493" t="inlineStr">
         <is>
           <t>39080</t>
         </is>
@@ -28831,7 +28861,7 @@
           <t>QUEMENEUR Malo</t>
         </is>
       </c>
-      <c r="U494" t="inlineStr">
+      <c r="X494" t="inlineStr">
         <is>
           <t>60403</t>
         </is>
@@ -28899,7 +28929,7 @@
           <t>TUNKA Ondrej</t>
         </is>
       </c>
-      <c r="U495" t="inlineStr">
+      <c r="X495" t="inlineStr">
         <is>
           <t>35947</t>
         </is>
@@ -28967,7 +28997,7 @@
           <t>KAUZER Peter</t>
         </is>
       </c>
-      <c r="U496" t="inlineStr">
+      <c r="X496" t="inlineStr">
         <is>
           <t>35589</t>
         </is>
@@ -29035,7 +29065,7 @@
           <t>DELFOUR Lucien</t>
         </is>
       </c>
-      <c r="U497" t="inlineStr">
+      <c r="X497" t="inlineStr">
         <is>
           <t>36537</t>
         </is>
@@ -29103,7 +29133,7 @@
           <t>CLARKE Joseph</t>
         </is>
       </c>
-      <c r="U498" t="inlineStr">
+      <c r="X498" t="inlineStr">
         <is>
           <t>35654</t>
         </is>
@@ -29171,7 +29201,7 @@
           <t>PRSKAVEC Jiri</t>
         </is>
       </c>
-      <c r="U499" t="inlineStr">
+      <c r="X499" t="inlineStr">
         <is>
           <t>35033</t>
         </is>
@@ -29239,7 +29269,7 @@
           <t>TRAVE Miquel</t>
         </is>
       </c>
-      <c r="U500" t="inlineStr">
+      <c r="X500" t="inlineStr">
         <is>
           <t>68998</t>
         </is>
@@ -29307,7 +29337,7 @@
           <t>DE GENNARO Giovanni</t>
         </is>
       </c>
-      <c r="U501" t="inlineStr">
+      <c r="X501" t="inlineStr">
         <is>
           <t>35244</t>
         </is>
@@ -29567,7 +29597,7 @@
           <t>SATKOVA Martina</t>
         </is>
       </c>
-      <c r="U506" t="inlineStr">
+      <c r="X506" t="inlineStr">
         <is>
           <t>42008</t>
         </is>
@@ -29698,7 +29728,7 @@
           <t>WOODS Kimberley</t>
         </is>
       </c>
-      <c r="U508" t="inlineStr">
+      <c r="X508" t="inlineStr">
         <is>
           <t>35650</t>
         </is>
@@ -29766,7 +29796,7 @@
           <t>MARX Alena</t>
         </is>
       </c>
-      <c r="U509" t="inlineStr">
+      <c r="X509" t="inlineStr">
         <is>
           <t>68844</t>
         </is>
@@ -29834,7 +29864,7 @@
           <t>BOUZIDI Carole</t>
         </is>
       </c>
-      <c r="U510" t="inlineStr">
+      <c r="X510" t="inlineStr">
         <is>
           <t>118428</t>
         </is>
@@ -29902,7 +29932,7 @@
           <t>TERCELJ Eva</t>
         </is>
       </c>
-      <c r="U511" t="inlineStr">
+      <c r="X511" t="inlineStr">
         <is>
           <t>36263</t>
         </is>
@@ -29970,7 +30000,7 @@
           <t>FUNK Ricarda</t>
         </is>
       </c>
-      <c r="U512" t="inlineStr">
+      <c r="X512" t="inlineStr">
         <is>
           <t>35122</t>
         </is>
@@ -30038,7 +30068,7 @@
           <t>WOLFFHARDT Viktoria</t>
         </is>
       </c>
-      <c r="U513" t="inlineStr">
+      <c r="X513" t="inlineStr">
         <is>
           <t>35303</t>
         </is>
@@ -30106,7 +30136,7 @@
           <t>STANOVSKA Sona</t>
         </is>
       </c>
-      <c r="U514" t="inlineStr">
+      <c r="X514" t="inlineStr">
         <is>
           <t>51647</t>
         </is>
@@ -30174,7 +30204,7 @@
           <t>VUITTON Emma</t>
         </is>
       </c>
-      <c r="U515" t="inlineStr">
+      <c r="X515" t="inlineStr">
         <is>
           <t>84126</t>
         </is>
@@ -30242,7 +30272,7 @@
           <t>ARREGUI Olatz</t>
         </is>
       </c>
-      <c r="U516" t="inlineStr">
+      <c r="X516" t="inlineStr">
         <is>
           <t>69083</t>
         </is>
@@ -30310,7 +30340,7 @@
           <t>PISTONI Lucia</t>
         </is>
       </c>
-      <c r="U517" t="inlineStr">
+      <c r="X517" t="inlineStr">
         <is>
           <t>104430</t>
         </is>
@@ -30378,7 +30408,7 @@
           <t>OGILVIE Sophie</t>
         </is>
       </c>
-      <c r="U518" t="inlineStr">
+      <c r="X518" t="inlineStr">
         <is>
           <t>53134</t>
         </is>
@@ -30446,7 +30476,7 @@
           <t>YAN Jiahua</t>
         </is>
       </c>
-      <c r="U519" t="inlineStr">
+      <c r="X519" t="inlineStr">
         <is>
           <t>43545</t>
         </is>
@@ -30514,7 +30544,7 @@
           <t>CHOURRAUT Maialen</t>
         </is>
       </c>
-      <c r="U520" t="inlineStr">
+      <c r="X520" t="inlineStr">
         <is>
           <t>35787</t>
         </is>
@@ -30582,7 +30612,7 @@
           <t>REINOSO Sofia</t>
         </is>
       </c>
-      <c r="U521" t="inlineStr">
+      <c r="X521" t="inlineStr">
         <is>
           <t>45745</t>
         </is>
@@ -30650,7 +30680,7 @@
           <t>ZWOLINSKA Klaudia</t>
         </is>
       </c>
-      <c r="U522" t="inlineStr">
+      <c r="X522" t="inlineStr">
         <is>
           <t>42027</t>
         </is>
@@ -30718,7 +30748,7 @@
           <t>WEGMAN Martina</t>
         </is>
       </c>
-      <c r="U523" t="inlineStr">
+      <c r="X523" t="inlineStr">
         <is>
           <t>35345</t>
         </is>
@@ -30786,7 +30816,7 @@
           <t>DORIA VILARRUBLA Monica</t>
         </is>
       </c>
-      <c r="U524" t="inlineStr">
+      <c r="X524" t="inlineStr">
         <is>
           <t>53051</t>
         </is>
@@ -30854,7 +30884,7 @@
           <t>SOMMERNES Iris</t>
         </is>
       </c>
-      <c r="U525" t="inlineStr">
+      <c r="X525" t="inlineStr">
         <is>
           <t>90378</t>
         </is>
@@ -30922,7 +30952,7 @@
           <t>BETTERIDGE Lois</t>
         </is>
       </c>
-      <c r="U526" t="inlineStr">
+      <c r="X526" t="inlineStr">
         <is>
           <t>60078</t>
         </is>
@@ -30990,7 +31020,7 @@
           <t>LAZKANO Miren</t>
         </is>
       </c>
-      <c r="U527" t="inlineStr">
+      <c r="X527" t="inlineStr">
         <is>
           <t>35748</t>
         </is>
@@ -31058,7 +31088,7 @@
           <t>LILIK Elena</t>
         </is>
       </c>
-      <c r="U528" t="inlineStr">
+      <c r="X528" t="inlineStr">
         <is>
           <t>51837</t>
         </is>
@@ -31126,7 +31156,7 @@
           <t>CASSINI Maria Luz</t>
         </is>
       </c>
-      <c r="U529" t="inlineStr">
+      <c r="X529" t="inlineStr">
         <is>
           <t>41627</t>
         </is>
@@ -31194,7 +31224,7 @@
           <t>SRIBAR Ria</t>
         </is>
       </c>
-      <c r="U530" t="inlineStr">
+      <c r="X530" t="inlineStr">
         <is>
           <t>75645</t>
         </is>
@@ -31262,7 +31292,7 @@
           <t>BAUDU Lucie</t>
         </is>
       </c>
-      <c r="U531" t="inlineStr">
+      <c r="X531" t="inlineStr">
         <is>
           <t>35669</t>
         </is>
@@ -31330,7 +31360,7 @@
           <t>FRANKLIN Mallory</t>
         </is>
       </c>
-      <c r="U532" t="inlineStr">
+      <c r="X532" t="inlineStr">
         <is>
           <t>35615</t>
         </is>
@@ -31398,7 +31428,7 @@
           <t>YAZAWA Aki</t>
         </is>
       </c>
-      <c r="U533" t="inlineStr">
+      <c r="X533" t="inlineStr">
         <is>
           <t>36486</t>
         </is>
@@ -31466,7 +31496,7 @@
           <t>FOX Noemie</t>
         </is>
       </c>
-      <c r="U534" t="inlineStr">
+      <c r="X534" t="inlineStr">
         <is>
           <t>44812</t>
         </is>
@@ -31534,7 +31564,7 @@
           <t>SATILA Ana</t>
         </is>
       </c>
-      <c r="U535" t="inlineStr">
+      <c r="X535" t="inlineStr">
         <is>
           <t>35327</t>
         </is>
@@ -31602,7 +31632,7 @@
           <t>PRIGENT Camille</t>
         </is>
       </c>
-      <c r="U536" t="inlineStr">
+      <c r="X536" t="inlineStr">
         <is>
           <t>41566</t>
         </is>
@@ -31670,7 +31700,7 @@
           <t>RAZEGHIAN Roxana</t>
         </is>
       </c>
-      <c r="U537" t="inlineStr">
+      <c r="X537" t="inlineStr">
         <is>
           <t>63124</t>
         </is>
@@ -31738,7 +31768,7 @@
           <t>PASIUT Michal</t>
         </is>
       </c>
-      <c r="U538" t="inlineStr">
+      <c r="X538" t="inlineStr">
         <is>
           <t>35095</t>
         </is>
@@ -31806,7 +31836,7 @@
           <t>DE COSTER Gabriel</t>
         </is>
       </c>
-      <c r="U539" t="inlineStr">
+      <c r="X539" t="inlineStr">
         <is>
           <t>68818</t>
         </is>
@@ -31874,7 +31904,7 @@
           <t>OCHOA Manuel</t>
         </is>
       </c>
-      <c r="U540" t="inlineStr">
+      <c r="X540" t="inlineStr">
         <is>
           <t>69081</t>
         </is>
@@ -31942,7 +31972,7 @@
           <t>LIU Chin-Han</t>
         </is>
       </c>
-      <c r="U541" t="inlineStr">
+      <c r="X541" t="inlineStr">
         <is>
           <t>51894</t>
         </is>
@@ -32010,7 +32040,7 @@
           <t>BALDONI Alex</t>
         </is>
       </c>
-      <c r="U542" t="inlineStr">
+      <c r="X542" t="inlineStr">
         <is>
           <t>94528</t>
         </is>
@@ -32078,7 +32108,7 @@
           <t>HENGST Stefan</t>
         </is>
       </c>
-      <c r="U543" t="inlineStr">
+      <c r="X543" t="inlineStr">
         <is>
           <t>39061</t>
         </is>
@@ -32146,7 +32176,7 @@
           <t>GONCALVES Pedro</t>
         </is>
       </c>
-      <c r="U544" t="inlineStr">
+      <c r="X544" t="inlineStr">
         <is>
           <t>38017</t>
         </is>
@@ -32214,7 +32244,7 @@
           <t>MCCREERY Alistair</t>
         </is>
       </c>
-      <c r="U545" t="inlineStr">
+      <c r="X545" t="inlineStr">
         <is>
           <t>60125</t>
         </is>
@@ -32282,7 +32312,7 @@
           <t>OHRSTROM Isak</t>
         </is>
       </c>
-      <c r="U546" t="inlineStr">
+      <c r="X546" t="inlineStr">
         <is>
           <t>35101</t>
         </is>
@@ -32350,7 +32380,7 @@
           <t>VIANELLO Marco</t>
         </is>
       </c>
-      <c r="U547" t="inlineStr">
+      <c r="X547" t="inlineStr">
         <is>
           <t>54910</t>
         </is>
@@ -32418,7 +32448,7 @@
           <t>PRINDIS Vit</t>
         </is>
       </c>
-      <c r="U548" t="inlineStr">
+      <c r="X548" t="inlineStr">
         <is>
           <t>35065</t>
         </is>
@@ -32486,7 +32516,7 @@
           <t>YU Haijie</t>
         </is>
       </c>
-      <c r="U549" t="inlineStr">
+      <c r="X549" t="inlineStr">
         <is>
           <t>118849</t>
         </is>
@@ -32554,7 +32584,7 @@
           <t>KUDER MARUSIC Vid</t>
         </is>
       </c>
-      <c r="U550" t="inlineStr">
+      <c r="X550" t="inlineStr">
         <is>
           <t>44342</t>
         </is>
@@ -32622,7 +32652,7 @@
           <t>FRIEDENSON Kaelin</t>
         </is>
       </c>
-      <c r="U551" t="inlineStr">
+      <c r="X551" t="inlineStr">
         <is>
           <t>87397</t>
         </is>
@@ -32690,7 +32720,7 @@
           <t>BUTCHER Finn</t>
         </is>
       </c>
-      <c r="U552" t="inlineStr">
+      <c r="X552" t="inlineStr">
         <is>
           <t>36663</t>
         </is>
@@ -32758,7 +32788,7 @@
           <t>CUNHA Joao</t>
         </is>
       </c>
-      <c r="U553" t="inlineStr">
+      <c r="X553" t="inlineStr">
         <is>
           <t>76853</t>
         </is>
@@ -32826,7 +32856,7 @@
           <t>HEGER Vojtech</t>
         </is>
       </c>
-      <c r="U554" t="inlineStr">
+      <c r="X554" t="inlineStr">
         <is>
           <t>68872</t>
         </is>
@@ -32894,7 +32924,7 @@
           <t>IVALDI Zeno</t>
         </is>
       </c>
-      <c r="U555" t="inlineStr">
+      <c r="X555" t="inlineStr">
         <is>
           <t>35480</t>
         </is>
@@ -32962,7 +32992,7 @@
           <t>LLORENTE David</t>
         </is>
       </c>
-      <c r="U556" t="inlineStr">
+      <c r="X556" t="inlineStr">
         <is>
           <t>51850</t>
         </is>
@@ -33030,7 +33060,7 @@
           <t>KULIKOV Alexandr</t>
         </is>
       </c>
-      <c r="U557" t="inlineStr">
+      <c r="X557" t="inlineStr">
         <is>
           <t>39679</t>
         </is>
@@ -33098,7 +33128,7 @@
           <t>POPE Benjamin</t>
         </is>
       </c>
-      <c r="U558" t="inlineStr">
+      <c r="X558" t="inlineStr">
         <is>
           <t>51753</t>
         </is>
@@ -33166,7 +33196,7 @@
           <t>LEITNER Mario</t>
         </is>
       </c>
-      <c r="U559" t="inlineStr">
+      <c r="X559" t="inlineStr">
         <is>
           <t>35546</t>
         </is>
@@ -33234,7 +33264,7 @@
           <t>CHAPPELL Etienne</t>
         </is>
       </c>
-      <c r="U560" t="inlineStr">
+      <c r="X560" t="inlineStr">
         <is>
           <t>75833</t>
         </is>
@@ -33302,7 +33332,7 @@
           <t>STANOVSKY Jakub</t>
         </is>
       </c>
-      <c r="U561" t="inlineStr">
+      <c r="X561" t="inlineStr">
         <is>
           <t>41781</t>
         </is>
@@ -33370,7 +33400,7 @@
           <t>CORTEZ Geronimo</t>
         </is>
       </c>
-      <c r="U562" t="inlineStr">
+      <c r="X562" t="inlineStr">
         <is>
           <t>51835</t>
         </is>
@@ -33438,7 +33468,7 @@
           <t>DESVIGNES Theo</t>
         </is>
       </c>
-      <c r="U563" t="inlineStr">
+      <c r="X563" t="inlineStr">
         <is>
           <t>84389</t>
         </is>
@@ -33506,7 +33536,7 @@
           <t>BOWERS Christopher</t>
         </is>
       </c>
-      <c r="U564" t="inlineStr">
+      <c r="X564" t="inlineStr">
         <is>
           <t>52010</t>
         </is>
@@ -33574,7 +33604,7 @@
           <t>UKALOVIC Thomas</t>
         </is>
       </c>
-      <c r="U565" t="inlineStr">
+      <c r="X565" t="inlineStr">
         <is>
           <t>93708</t>
         </is>
@@ -33642,7 +33672,7 @@
           <t>KANCLER Tine</t>
         </is>
       </c>
-      <c r="U566" t="inlineStr">
+      <c r="X566" t="inlineStr">
         <is>
           <t>51813</t>
         </is>
@@ -33710,7 +33740,7 @@
           <t>MARX Dimitri</t>
         </is>
       </c>
-      <c r="U567" t="inlineStr">
+      <c r="X567" t="inlineStr">
         <is>
           <t>60326</t>
         </is>
@@ -33778,7 +33808,7 @@
           <t>CRESPO Joan</t>
         </is>
       </c>
-      <c r="U568" t="inlineStr">
+      <c r="X568" t="inlineStr">
         <is>
           <t>35749</t>
         </is>
@@ -33846,7 +33876,7 @@
           <t>SOVKO Serhii</t>
         </is>
       </c>
-      <c r="U569" t="inlineStr">
+      <c r="X569" t="inlineStr">
         <is>
           <t>94235</t>
         </is>
@@ -34111,7 +34141,7 @@
           <t>LYU Minzhen</t>
         </is>
       </c>
-      <c r="U574" t="inlineStr">
+      <c r="X574" t="inlineStr">
         <is>
           <t>75379</t>
         </is>
@@ -34169,7 +34199,7 @@
           <t>BETTERIDGE Lois</t>
         </is>
       </c>
-      <c r="U575" t="inlineStr">
+      <c r="X575" t="inlineStr">
         <is>
           <t>60078</t>
         </is>
@@ -34227,7 +34257,7 @@
           <t>PELLICER CHICA Laura</t>
         </is>
       </c>
-      <c r="U576" t="inlineStr">
+      <c r="X576" t="inlineStr">
         <is>
           <t>43129</t>
         </is>
@@ -34285,7 +34315,7 @@
           <t>FOX Noemie</t>
         </is>
       </c>
-      <c r="U577" t="inlineStr">
+      <c r="X577" t="inlineStr">
         <is>
           <t>44812</t>
         </is>
@@ -34343,7 +34373,7 @@
           <t>BAYN Nele</t>
         </is>
       </c>
-      <c r="U578" t="inlineStr">
+      <c r="X578" t="inlineStr">
         <is>
           <t>75442</t>
         </is>
@@ -34401,7 +34431,7 @@
           <t>MILLER Ellis</t>
         </is>
       </c>
-      <c r="U579" t="inlineStr">
+      <c r="X579" t="inlineStr">
         <is>
           <t>75828</t>
         </is>
@@ -34459,7 +34489,7 @@
           <t>WOLFFHARDT Viktoria</t>
         </is>
       </c>
-      <c r="U580" t="inlineStr">
+      <c r="X580" t="inlineStr">
         <is>
           <t>35303</t>
         </is>
@@ -34517,7 +34547,7 @@
           <t>LUKNAROVA Emanuela</t>
         </is>
       </c>
-      <c r="U581" t="inlineStr">
+      <c r="X581" t="inlineStr">
         <is>
           <t>76973</t>
         </is>
@@ -34575,7 +34605,7 @@
           <t>BAUDU Lucie</t>
         </is>
       </c>
-      <c r="U582" t="inlineStr">
+      <c r="X582" t="inlineStr">
         <is>
           <t>35669</t>
         </is>
@@ -34633,7 +34663,7 @@
           <t>PANKOVA Zuzana</t>
         </is>
       </c>
-      <c r="U583" t="inlineStr">
+      <c r="X583" t="inlineStr">
         <is>
           <t>93906</t>
         </is>
@@ -34691,7 +34721,7 @@
           <t>US Viktoriia</t>
         </is>
       </c>
-      <c r="U584" t="inlineStr">
+      <c r="X584" t="inlineStr">
         <is>
           <t>35528</t>
         </is>
@@ -34749,7 +34779,7 @@
           <t>MARX Alena</t>
         </is>
       </c>
-      <c r="U585" t="inlineStr">
+      <c r="X585" t="inlineStr">
         <is>
           <t>68844</t>
         </is>
@@ -34807,7 +34837,7 @@
           <t>BERTONCELLI Marta</t>
         </is>
       </c>
-      <c r="U586" t="inlineStr">
+      <c r="X586" t="inlineStr">
         <is>
           <t>71982</t>
         </is>
@@ -34865,7 +34895,7 @@
           <t>BORGHI Elena</t>
         </is>
       </c>
-      <c r="U587" t="inlineStr">
+      <c r="X587" t="inlineStr">
         <is>
           <t>75493</t>
         </is>
@@ -34923,7 +34953,7 @@
           <t>WOODS Kimberley</t>
         </is>
       </c>
-      <c r="U588" t="inlineStr">
+      <c r="X588" t="inlineStr">
         <is>
           <t>35650</t>
         </is>
@@ -34981,7 +35011,7 @@
           <t>ROISIN Laurene</t>
         </is>
       </c>
-      <c r="U589" t="inlineStr">
+      <c r="X589" t="inlineStr">
         <is>
           <t>76198</t>
         </is>
@@ -35039,7 +35069,7 @@
           <t>SATILA Ana</t>
         </is>
       </c>
-      <c r="U590" t="inlineStr">
+      <c r="X590" t="inlineStr">
         <is>
           <t>35327</t>
         </is>
@@ -35097,7 +35127,7 @@
           <t>LAMEIRO Ainhoa</t>
         </is>
       </c>
-      <c r="U591" t="inlineStr">
+      <c r="X591" t="inlineStr">
         <is>
           <t>69042</t>
         </is>
@@ -35155,7 +35185,7 @@
           <t>OLAZABAL Klara</t>
         </is>
       </c>
-      <c r="U592" t="inlineStr">
+      <c r="X592" t="inlineStr">
         <is>
           <t>43985</t>
         </is>
@@ -35213,7 +35243,7 @@
           <t>SATKOVA Martina</t>
         </is>
       </c>
-      <c r="U593" t="inlineStr">
+      <c r="X593" t="inlineStr">
         <is>
           <t>42008</t>
         </is>
@@ -35271,7 +35301,7 @@
           <t>NOVAK Lea</t>
         </is>
       </c>
-      <c r="U594" t="inlineStr">
+      <c r="X594" t="inlineStr">
         <is>
           <t>60323</t>
         </is>
@@ -35329,7 +35359,7 @@
           <t>FISEROVA Tereza</t>
         </is>
       </c>
-      <c r="U595" t="inlineStr">
+      <c r="X595" t="inlineStr">
         <is>
           <t>42016</t>
         </is>
@@ -35387,7 +35417,7 @@
           <t>LILIK Elena</t>
         </is>
       </c>
-      <c r="U596" t="inlineStr">
+      <c r="X596" t="inlineStr">
         <is>
           <t>51837</t>
         </is>
@@ -35445,7 +35475,7 @@
           <t>LAZKANO Miren</t>
         </is>
       </c>
-      <c r="U597" t="inlineStr">
+      <c r="X597" t="inlineStr">
         <is>
           <t>35748</t>
         </is>
@@ -35503,7 +35533,7 @@
           <t>SATKOVA Gabriela</t>
         </is>
       </c>
-      <c r="U598" t="inlineStr">
+      <c r="X598" t="inlineStr">
         <is>
           <t>68786</t>
         </is>
@@ -35561,7 +35591,7 @@
           <t>HERZOG Andrea</t>
         </is>
       </c>
-      <c r="U599" t="inlineStr">
+      <c r="X599" t="inlineStr">
         <is>
           <t>55099</t>
         </is>
@@ -35619,7 +35649,7 @@
           <t>FRANKLIN Mallory</t>
         </is>
       </c>
-      <c r="U600" t="inlineStr">
+      <c r="X600" t="inlineStr">
         <is>
           <t>35615</t>
         </is>
@@ -35677,7 +35707,7 @@
           <t>DORIA VILARRUBLA Monica</t>
         </is>
       </c>
-      <c r="U601" t="inlineStr">
+      <c r="X601" t="inlineStr">
         <is>
           <t>53051</t>
         </is>
@@ -35735,7 +35765,7 @@
           <t>DELASSUS Marjorie</t>
         </is>
       </c>
-      <c r="U602" t="inlineStr">
+      <c r="X602" t="inlineStr">
         <is>
           <t>71964</t>
         </is>
@@ -35793,7 +35823,7 @@
           <t>FOX Jessica</t>
         </is>
       </c>
-      <c r="U603" t="inlineStr">
+      <c r="X603" t="inlineStr">
         <is>
           <t>36526</t>
         </is>
@@ -35851,7 +35881,7 @@
           <t>HENDRICK Robert</t>
         </is>
       </c>
-      <c r="U604" t="inlineStr">
+      <c r="X604" t="inlineStr">
         <is>
           <t>43002</t>
         </is>
@@ -35909,7 +35939,7 @@
           <t>SASAKI Shota</t>
         </is>
       </c>
-      <c r="U605" t="inlineStr">
+      <c r="X605" t="inlineStr">
         <is>
           <t>41610</t>
         </is>
@@ -35967,7 +35997,7 @@
           <t>CRAWFORD Brodie</t>
         </is>
       </c>
-      <c r="U606" t="inlineStr">
+      <c r="X606" t="inlineStr">
         <is>
           <t>38436</t>
         </is>
@@ -36025,7 +36055,7 @@
           <t>TRUMMER Timo</t>
         </is>
       </c>
-      <c r="U607" t="inlineStr">
+      <c r="X607" t="inlineStr">
         <is>
           <t>41599</t>
         </is>
@@ -36083,7 +36113,7 @@
           <t>COCHRANE Jake</t>
         </is>
       </c>
-      <c r="U608" t="inlineStr">
+      <c r="X608" t="inlineStr">
         <is>
           <t>60124</t>
         </is>
@@ -36141,7 +36171,7 @@
           <t>BASSETT Kaylen</t>
         </is>
       </c>
-      <c r="U609" t="inlineStr">
+      <c r="X609" t="inlineStr">
         <is>
           <t>75376</t>
         </is>
@@ -36199,7 +36229,7 @@
           <t>HEGER Vojtech</t>
         </is>
       </c>
-      <c r="U610" t="inlineStr">
+      <c r="X610" t="inlineStr">
         <is>
           <t>68872</t>
         </is>
@@ -36257,7 +36287,7 @@
           <t>BERCIC Anze</t>
         </is>
       </c>
-      <c r="U611" t="inlineStr">
+      <c r="X611" t="inlineStr">
         <is>
           <t>36253</t>
         </is>
@@ -36315,7 +36345,7 @@
           <t>BURGESS Adam</t>
         </is>
       </c>
-      <c r="U612" t="inlineStr">
+      <c r="X612" t="inlineStr">
         <is>
           <t>35647</t>
         </is>
@@ -36373,7 +36403,7 @@
           <t>KOECHLIN Thomas</t>
         </is>
       </c>
-      <c r="U613" t="inlineStr">
+      <c r="X613" t="inlineStr">
         <is>
           <t>35419</t>
         </is>
@@ -36431,7 +36461,7 @@
           <t>CARTER Tristan</t>
         </is>
       </c>
-      <c r="U614" t="inlineStr">
+      <c r="X614" t="inlineStr">
         <is>
           <t>51890</t>
         </is>
@@ -36489,7 +36519,7 @@
           <t>MIRGORODSKY Marko</t>
         </is>
       </c>
-      <c r="U615" t="inlineStr">
+      <c r="X615" t="inlineStr">
         <is>
           <t>42019</t>
         </is>
@@ -36547,7 +36577,7 @@
           <t>JEGOU Liam</t>
         </is>
       </c>
-      <c r="U616" t="inlineStr">
+      <c r="X616" t="inlineStr">
         <is>
           <t>35820</t>
         </is>
@@ -36605,7 +36635,7 @@
           <t>BENUS Matej</t>
         </is>
       </c>
-      <c r="U617" t="inlineStr">
+      <c r="X617" t="inlineStr">
         <is>
           <t>35353</t>
         </is>
@@ -36663,7 +36693,7 @@
           <t>FERNANDEZ Luis</t>
         </is>
       </c>
-      <c r="U618" t="inlineStr">
+      <c r="X618" t="inlineStr">
         <is>
           <t>51851</t>
         </is>
@@ -36721,7 +36751,7 @@
           <t>LOKKEN Zachary</t>
         </is>
       </c>
-      <c r="U619" t="inlineStr">
+      <c r="X619" t="inlineStr">
         <is>
           <t>35069</t>
         </is>
@@ -36779,7 +36809,7 @@
           <t>WESTLEY Ryan</t>
         </is>
       </c>
-      <c r="U620" t="inlineStr">
+      <c r="X620" t="inlineStr">
         <is>
           <t>35651</t>
         </is>
@@ -36837,7 +36867,7 @@
           <t>GARGAUD CHANUT Denis</t>
         </is>
       </c>
-      <c r="U621" t="inlineStr">
+      <c r="X621" t="inlineStr">
         <is>
           <t>35177</t>
         </is>
@@ -36895,7 +36925,7 @@
           <t>HEDWIG Grzegorz</t>
         </is>
       </c>
-      <c r="U622" t="inlineStr">
+      <c r="X622" t="inlineStr">
         <is>
           <t>35465</t>
         </is>
@@ -36953,7 +36983,7 @@
           <t>TUCHSCHERER Lennard</t>
         </is>
       </c>
-      <c r="U623" t="inlineStr">
+      <c r="X623" t="inlineStr">
         <is>
           <t>60090</t>
         </is>
@@ -37011,7 +37041,7 @@
           <t>CHALOUPKA Vaclav</t>
         </is>
       </c>
-      <c r="U624" t="inlineStr">
+      <c r="X624" t="inlineStr">
         <is>
           <t>51648</t>
         </is>
@@ -37069,7 +37099,7 @@
           <t>TRAVE Miquel</t>
         </is>
       </c>
-      <c r="U625" t="inlineStr">
+      <c r="X625" t="inlineStr">
         <is>
           <t>68998</t>
         </is>
@@ -37127,7 +37157,7 @@
           <t>COLAZINGARI Roberto</t>
         </is>
       </c>
-      <c r="U626" t="inlineStr">
+      <c r="X626" t="inlineStr">
         <is>
           <t>35223</t>
         </is>
@@ -37185,7 +37215,7 @@
           <t>ROHAN Lukas</t>
         </is>
       </c>
-      <c r="U627" t="inlineStr">
+      <c r="X627" t="inlineStr">
         <is>
           <t>36114</t>
         </is>
@@ -37243,7 +37273,7 @@
           <t>DEBLIQUY Mewen</t>
         </is>
       </c>
-      <c r="U628" t="inlineStr">
+      <c r="X628" t="inlineStr">
         <is>
           <t>88656</t>
         </is>
@@ -37301,7 +37331,7 @@
           <t>CECCON Paolo</t>
         </is>
       </c>
-      <c r="U629" t="inlineStr">
+      <c r="X629" t="inlineStr">
         <is>
           <t>39903</t>
         </is>
@@ -37359,7 +37389,7 @@
           <t>GESTIN Nicolas</t>
         </is>
       </c>
-      <c r="U630" t="inlineStr">
+      <c r="X630" t="inlineStr">
         <is>
           <t>71961</t>
         </is>
@@ -37417,7 +37447,7 @@
           <t>IVALDI Raffaello</t>
         </is>
       </c>
-      <c r="U631" t="inlineStr">
+      <c r="X631" t="inlineStr">
         <is>
           <t>35227</t>
         </is>
@@ -37475,7 +37505,7 @@
           <t>SAVSEK Benjamin</t>
         </is>
       </c>
-      <c r="U632" t="inlineStr">
+      <c r="X632" t="inlineStr">
         <is>
           <t>36218</t>
         </is>
@@ -37533,7 +37563,7 @@
           <t>BOZIC Luka</t>
         </is>
       </c>
-      <c r="U633" t="inlineStr">
+      <c r="X633" t="inlineStr">
         <is>
           <t>36269</t>
         </is>
@@ -37601,7 +37631,7 @@
           <t>SATILA Ana</t>
         </is>
       </c>
-      <c r="U634" t="inlineStr">
+      <c r="X634" t="inlineStr">
         <is>
           <t>35327</t>
         </is>
@@ -37669,7 +37699,7 @@
           <t>BORGHI Elena</t>
         </is>
       </c>
-      <c r="U635" t="inlineStr">
+      <c r="X635" t="inlineStr">
         <is>
           <t>75493</t>
         </is>
@@ -37737,7 +37767,7 @@
           <t>LILIK Elena</t>
         </is>
       </c>
-      <c r="U636" t="inlineStr">
+      <c r="X636" t="inlineStr">
         <is>
           <t>51837</t>
         </is>
@@ -37805,7 +37835,7 @@
           <t>LAMEIRO Ainhoa</t>
         </is>
       </c>
-      <c r="U637" t="inlineStr">
+      <c r="X637" t="inlineStr">
         <is>
           <t>69042</t>
         </is>
@@ -37873,7 +37903,7 @@
           <t>FISEROVA Tereza</t>
         </is>
       </c>
-      <c r="U638" t="inlineStr">
+      <c r="X638" t="inlineStr">
         <is>
           <t>42016</t>
         </is>
@@ -37941,7 +37971,7 @@
           <t>HERZOG Andrea</t>
         </is>
       </c>
-      <c r="U639" t="inlineStr">
+      <c r="X639" t="inlineStr">
         <is>
           <t>55099</t>
         </is>
@@ -38009,7 +38039,7 @@
           <t>SATKOVA Gabriela</t>
         </is>
       </c>
-      <c r="U640" t="inlineStr">
+      <c r="X640" t="inlineStr">
         <is>
           <t>68786</t>
         </is>
@@ -38077,7 +38107,7 @@
           <t>DELASSUS Marjorie</t>
         </is>
       </c>
-      <c r="U641" t="inlineStr">
+      <c r="X641" t="inlineStr">
         <is>
           <t>71964</t>
         </is>
@@ -38145,7 +38175,7 @@
           <t>DORIA VILARRUBLA Monica</t>
         </is>
       </c>
-      <c r="U642" t="inlineStr">
+      <c r="X642" t="inlineStr">
         <is>
           <t>53051</t>
         </is>
@@ -38213,7 +38243,7 @@
           <t>FOX Jessica</t>
         </is>
       </c>
-      <c r="U643" t="inlineStr">
+      <c r="X643" t="inlineStr">
         <is>
           <t>36526</t>
         </is>
@@ -38281,7 +38311,7 @@
           <t>BERCIC Anze</t>
         </is>
       </c>
-      <c r="U644" t="inlineStr">
+      <c r="X644" t="inlineStr">
         <is>
           <t>36253</t>
         </is>
@@ -38349,7 +38379,7 @@
           <t>WESTLEY Ryan</t>
         </is>
       </c>
-      <c r="U645" t="inlineStr">
+      <c r="X645" t="inlineStr">
         <is>
           <t>35651</t>
         </is>
@@ -38417,7 +38447,7 @@
           <t>BURGESS Adam</t>
         </is>
       </c>
-      <c r="U646" t="inlineStr">
+      <c r="X646" t="inlineStr">
         <is>
           <t>35647</t>
         </is>
@@ -38485,7 +38515,7 @@
           <t>COLAZINGARI Roberto</t>
         </is>
       </c>
-      <c r="U647" t="inlineStr">
+      <c r="X647" t="inlineStr">
         <is>
           <t>35223</t>
         </is>
@@ -38553,7 +38583,7 @@
           <t>BENUS Matej</t>
         </is>
       </c>
-      <c r="U648" t="inlineStr">
+      <c r="X648" t="inlineStr">
         <is>
           <t>35353</t>
         </is>
@@ -38621,7 +38651,7 @@
           <t>GESTIN Nicolas</t>
         </is>
       </c>
-      <c r="U649" t="inlineStr">
+      <c r="X649" t="inlineStr">
         <is>
           <t>71961</t>
         </is>
@@ -38689,7 +38719,7 @@
           <t>BOZIC Luka</t>
         </is>
       </c>
-      <c r="U650" t="inlineStr">
+      <c r="X650" t="inlineStr">
         <is>
           <t>36269</t>
         </is>
@@ -38757,7 +38787,7 @@
           <t>CHALOUPKA Vaclav</t>
         </is>
       </c>
-      <c r="U651" t="inlineStr">
+      <c r="X651" t="inlineStr">
         <is>
           <t>51648</t>
         </is>
@@ -38825,7 +38855,7 @@
           <t>IVALDI Raffaello</t>
         </is>
       </c>
-      <c r="U652" t="inlineStr">
+      <c r="X652" t="inlineStr">
         <is>
           <t>35227</t>
         </is>
@@ -38893,7 +38923,7 @@
           <t>TRAVE Miquel</t>
         </is>
       </c>
-      <c r="U653" t="inlineStr">
+      <c r="X653" t="inlineStr">
         <is>
           <t>68998</t>
         </is>
@@ -38961,7 +38991,7 @@
           <t>FUNK Ricarda</t>
         </is>
       </c>
-      <c r="U654" t="inlineStr">
+      <c r="X654" t="inlineStr">
         <is>
           <t>35122</t>
         </is>
@@ -39029,7 +39059,7 @@
           <t>MARX Alena</t>
         </is>
       </c>
-      <c r="U655" t="inlineStr">
+      <c r="X655" t="inlineStr">
         <is>
           <t>68844</t>
         </is>
@@ -39097,7 +39127,7 @@
           <t>TERCELJ Eva</t>
         </is>
       </c>
-      <c r="U656" t="inlineStr">
+      <c r="X656" t="inlineStr">
         <is>
           <t>36263</t>
         </is>
@@ -39228,7 +39258,7 @@
           <t>YAN Jiahua</t>
         </is>
       </c>
-      <c r="U658" t="inlineStr">
+      <c r="X658" t="inlineStr">
         <is>
           <t>43545</t>
         </is>
@@ -39296,7 +39326,7 @@
           <t>ARREGUI Olatz</t>
         </is>
       </c>
-      <c r="U659" t="inlineStr">
+      <c r="X659" t="inlineStr">
         <is>
           <t>69083</t>
         </is>
@@ -39364,7 +39394,7 @@
           <t>CHOURRAUT Maialen</t>
         </is>
       </c>
-      <c r="U660" t="inlineStr">
+      <c r="X660" t="inlineStr">
         <is>
           <t>35787</t>
         </is>
@@ -39432,7 +39462,7 @@
           <t>STANOVSKA Sona</t>
         </is>
       </c>
-      <c r="U661" t="inlineStr">
+      <c r="X661" t="inlineStr">
         <is>
           <t>51647</t>
         </is>
@@ -39500,7 +39530,7 @@
           <t>LAZKANO Miren</t>
         </is>
       </c>
-      <c r="U662" t="inlineStr">
+      <c r="X662" t="inlineStr">
         <is>
           <t>35748</t>
         </is>
@@ -39568,7 +39598,7 @@
           <t>ZWOLINSKA Klaudia</t>
         </is>
       </c>
-      <c r="U663" t="inlineStr">
+      <c r="X663" t="inlineStr">
         <is>
           <t>42027</t>
         </is>
@@ -39636,7 +39666,7 @@
           <t>LILIK Elena</t>
         </is>
       </c>
-      <c r="U664" t="inlineStr">
+      <c r="X664" t="inlineStr">
         <is>
           <t>51837</t>
         </is>
@@ -39704,7 +39734,7 @@
           <t>WEGMAN Martina</t>
         </is>
       </c>
-      <c r="U665" t="inlineStr">
+      <c r="X665" t="inlineStr">
         <is>
           <t>35345</t>
         </is>
@@ -39772,7 +39802,7 @@
           <t>BAUDU Lucie</t>
         </is>
       </c>
-      <c r="U666" t="inlineStr">
+      <c r="X666" t="inlineStr">
         <is>
           <t>35669</t>
         </is>
@@ -39840,7 +39870,7 @@
           <t>FRANKLIN Mallory</t>
         </is>
       </c>
-      <c r="U667" t="inlineStr">
+      <c r="X667" t="inlineStr">
         <is>
           <t>35615</t>
         </is>
@@ -39908,7 +39938,7 @@
           <t>PRIGENT Camille</t>
         </is>
       </c>
-      <c r="U668" t="inlineStr">
+      <c r="X668" t="inlineStr">
         <is>
           <t>41566</t>
         </is>
@@ -39976,7 +40006,7 @@
           <t>SATILA Ana</t>
         </is>
       </c>
-      <c r="U669" t="inlineStr">
+      <c r="X669" t="inlineStr">
         <is>
           <t>35327</t>
         </is>
@@ -40044,7 +40074,7 @@
           <t>PASIUT Michal</t>
         </is>
       </c>
-      <c r="U670" t="inlineStr">
+      <c r="X670" t="inlineStr">
         <is>
           <t>35095</t>
         </is>
@@ -40112,7 +40142,7 @@
           <t>HENGST Stefan</t>
         </is>
       </c>
-      <c r="U671" t="inlineStr">
+      <c r="X671" t="inlineStr">
         <is>
           <t>39061</t>
         </is>
@@ -40180,7 +40210,7 @@
           <t>OCHOA Manuel</t>
         </is>
       </c>
-      <c r="U672" t="inlineStr">
+      <c r="X672" t="inlineStr">
         <is>
           <t>69081</t>
         </is>
@@ -40248,7 +40278,7 @@
           <t>BALDONI Alex</t>
         </is>
       </c>
-      <c r="U673" t="inlineStr">
+      <c r="X673" t="inlineStr">
         <is>
           <t>94528</t>
         </is>
@@ -40316,7 +40346,7 @@
           <t>KUDER MARUSIC Vid</t>
         </is>
       </c>
-      <c r="U674" t="inlineStr">
+      <c r="X674" t="inlineStr">
         <is>
           <t>44342</t>
         </is>
@@ -40384,7 +40414,7 @@
           <t>FRIEDENSON Kaelin</t>
         </is>
       </c>
-      <c r="U675" t="inlineStr">
+      <c r="X675" t="inlineStr">
         <is>
           <t>87397</t>
         </is>
@@ -40452,7 +40482,7 @@
           <t>PRINDIS Vit</t>
         </is>
       </c>
-      <c r="U676" t="inlineStr">
+      <c r="X676" t="inlineStr">
         <is>
           <t>35065</t>
         </is>
@@ -40520,7 +40550,7 @@
           <t>YU Haijie</t>
         </is>
       </c>
-      <c r="U677" t="inlineStr">
+      <c r="X677" t="inlineStr">
         <is>
           <t>118849</t>
         </is>
@@ -40588,7 +40618,7 @@
           <t>HEGER Vojtech</t>
         </is>
       </c>
-      <c r="U678" t="inlineStr">
+      <c r="X678" t="inlineStr">
         <is>
           <t>68872</t>
         </is>
@@ -40656,7 +40686,7 @@
           <t>LEITNER Mario</t>
         </is>
       </c>
-      <c r="U679" t="inlineStr">
+      <c r="X679" t="inlineStr">
         <is>
           <t>35546</t>
         </is>
@@ -40724,7 +40754,7 @@
           <t>LLORENTE David</t>
         </is>
       </c>
-      <c r="U680" t="inlineStr">
+      <c r="X680" t="inlineStr">
         <is>
           <t>51850</t>
         </is>
@@ -40792,7 +40822,7 @@
           <t>STANOVSKY Jakub</t>
         </is>
       </c>
-      <c r="U681" t="inlineStr">
+      <c r="X681" t="inlineStr">
         <is>
           <t>41781</t>
         </is>
@@ -40860,7 +40890,7 @@
           <t>KANCLER Tine</t>
         </is>
       </c>
-      <c r="U682" t="inlineStr">
+      <c r="X682" t="inlineStr">
         <is>
           <t>51813</t>
         </is>
@@ -40928,7 +40958,7 @@
           <t>MARX Dimitri</t>
         </is>
       </c>
-      <c r="U683" t="inlineStr">
+      <c r="X683" t="inlineStr">
         <is>
           <t>60326</t>
         </is>
@@ -40996,7 +41026,7 @@
           <t>DESVIGNES Theo</t>
         </is>
       </c>
-      <c r="U684" t="inlineStr">
+      <c r="X684" t="inlineStr">
         <is>
           <t>84389</t>
         </is>
@@ -41064,7 +41094,7 @@
           <t>CORTEZ Geronimo</t>
         </is>
       </c>
-      <c r="U685" t="inlineStr">
+      <c r="X685" t="inlineStr">
         <is>
           <t>51835</t>
         </is>
@@ -41132,7 +41162,7 @@
           <t>TERCELJ Eva</t>
         </is>
       </c>
-      <c r="U686" t="inlineStr">
+      <c r="X686" t="inlineStr">
         <is>
           <t>36263</t>
         </is>
@@ -41263,7 +41293,7 @@
           <t>ARREGUI Olatz</t>
         </is>
       </c>
-      <c r="U688" t="inlineStr">
+      <c r="X688" t="inlineStr">
         <is>
           <t>69083</t>
         </is>
@@ -41331,7 +41361,7 @@
           <t>STANOVSKA Sona</t>
         </is>
       </c>
-      <c r="U689" t="inlineStr">
+      <c r="X689" t="inlineStr">
         <is>
           <t>51647</t>
         </is>
@@ -41399,7 +41429,7 @@
           <t>LILIK Elena</t>
         </is>
       </c>
-      <c r="U690" t="inlineStr">
+      <c r="X690" t="inlineStr">
         <is>
           <t>51837</t>
         </is>
@@ -41467,7 +41497,7 @@
           <t>LAZKANO Miren</t>
         </is>
       </c>
-      <c r="U691" t="inlineStr">
+      <c r="X691" t="inlineStr">
         <is>
           <t>35748</t>
         </is>
@@ -41535,7 +41565,7 @@
           <t>PRIGENT Camille</t>
         </is>
       </c>
-      <c r="U692" t="inlineStr">
+      <c r="X692" t="inlineStr">
         <is>
           <t>41566</t>
         </is>
@@ -41603,7 +41633,7 @@
           <t>FRANKLIN Mallory</t>
         </is>
       </c>
-      <c r="U693" t="inlineStr">
+      <c r="X693" t="inlineStr">
         <is>
           <t>35615</t>
         </is>
@@ -41671,7 +41701,7 @@
           <t>OCHOA Manuel</t>
         </is>
       </c>
-      <c r="U694" t="inlineStr">
+      <c r="X694" t="inlineStr">
         <is>
           <t>69081</t>
         </is>
@@ -41739,7 +41769,7 @@
           <t>PASIUT Michal</t>
         </is>
       </c>
-      <c r="U695" t="inlineStr">
+      <c r="X695" t="inlineStr">
         <is>
           <t>35095</t>
         </is>
@@ -41807,7 +41837,7 @@
           <t>FRIEDENSON Kaelin</t>
         </is>
       </c>
-      <c r="U696" t="inlineStr">
+      <c r="X696" t="inlineStr">
         <is>
           <t>87397</t>
         </is>
@@ -41875,7 +41905,7 @@
           <t>PRINDIS Vit</t>
         </is>
       </c>
-      <c r="U697" t="inlineStr">
+      <c r="X697" t="inlineStr">
         <is>
           <t>35065</t>
         </is>
@@ -41943,7 +41973,7 @@
           <t>DESVIGNES Theo</t>
         </is>
       </c>
-      <c r="U698" t="inlineStr">
+      <c r="X698" t="inlineStr">
         <is>
           <t>84389</t>
         </is>
@@ -42011,7 +42041,7 @@
           <t>MARX Dimitri</t>
         </is>
       </c>
-      <c r="U699" t="inlineStr">
+      <c r="X699" t="inlineStr">
         <is>
           <t>60326</t>
         </is>
@@ -42079,7 +42109,7 @@
           <t>LLORENTE David</t>
         </is>
       </c>
-      <c r="U700" t="inlineStr">
+      <c r="X700" t="inlineStr">
         <is>
           <t>51850</t>
         </is>
@@ -42147,7 +42177,7 @@
           <t>HEGER Vojtech</t>
         </is>
       </c>
-      <c r="U701" t="inlineStr">
+      <c r="X701" t="inlineStr">
         <is>
           <t>68872</t>
         </is>
@@ -42225,7 +42255,7 @@
           <t>ARREGUI Olatz</t>
         </is>
       </c>
-      <c r="U702" t="inlineStr">
+      <c r="X702" t="inlineStr">
         <is>
           <t>69083</t>
         </is>
@@ -42303,7 +42333,7 @@
           <t>TERCELJ Eva</t>
         </is>
       </c>
-      <c r="U703" t="inlineStr">
+      <c r="X703" t="inlineStr">
         <is>
           <t>36263</t>
         </is>
@@ -42381,7 +42411,7 @@
           <t>LILIK Elena</t>
         </is>
       </c>
-      <c r="U704" t="inlineStr">
+      <c r="X704" t="inlineStr">
         <is>
           <t>51837</t>
         </is>
@@ -42459,7 +42489,7 @@
           <t>FRANKLIN Mallory</t>
         </is>
       </c>
-      <c r="U705" t="inlineStr">
+      <c r="X705" t="inlineStr">
         <is>
           <t>35615</t>
         </is>
@@ -42537,7 +42567,7 @@
           <t>PRINDIS Vit</t>
         </is>
       </c>
-      <c r="U706" t="inlineStr">
+      <c r="X706" t="inlineStr">
         <is>
           <t>35065</t>
         </is>
@@ -42615,7 +42645,7 @@
           <t>DESVIGNES Theo</t>
         </is>
       </c>
-      <c r="U707" t="inlineStr">
+      <c r="X707" t="inlineStr">
         <is>
           <t>84389</t>
         </is>
@@ -42693,7 +42723,7 @@
           <t>OCHOA Manuel</t>
         </is>
       </c>
-      <c r="U708" t="inlineStr">
+      <c r="X708" t="inlineStr">
         <is>
           <t>69081</t>
         </is>
@@ -42771,7 +42801,7 @@
           <t>HEGER Vojtech</t>
         </is>
       </c>
-      <c r="U709" t="inlineStr">
+      <c r="X709" t="inlineStr">
         <is>
           <t>68872</t>
         </is>

--- a/events/LaSeu_2022_WC/LaSeu_2022_WC_start.xlsx
+++ b/events/LaSeu_2022_WC/LaSeu_2022_WC_start.xlsx
@@ -29665,6 +29665,11 @@
           <t>FISEROVA Tereza</t>
         </is>
       </c>
+      <c r="X507" t="inlineStr">
+        <is>
+          <t>42016</t>
+        </is>
+      </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
@@ -39195,6 +39200,11 @@
           <t>FISEROVA Tereza</t>
         </is>
       </c>
+      <c r="X657" t="inlineStr">
+        <is>
+          <t>42016</t>
+        </is>
+      </c>
     </row>
     <row r="658">
       <c r="A658" t="inlineStr">
@@ -41228,6 +41238,11 @@
       <c r="R687" t="inlineStr">
         <is>
           <t>FISEROVA Tereza</t>
+        </is>
+      </c>
+      <c r="X687" t="inlineStr">
+        <is>
+          <t>42016</t>
         </is>
       </c>
     </row>
